--- a/data/customer-import/tier2_invented_parents.xlsx
+++ b/data/customer-import/tier2_invented_parents.xlsx
@@ -36291,12 +36291,12 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>SJMHS</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E406" t="inlineStr"/>
@@ -36478,7 +36478,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr"/>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr"/>
@@ -36662,7 +36662,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr"/>
@@ -36754,7 +36754,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr"/>
@@ -36846,7 +36846,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -36938,7 +36938,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
@@ -37030,7 +37030,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -37122,7 +37122,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr"/>
@@ -37214,7 +37214,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
@@ -37306,7 +37306,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr"/>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
@@ -37490,7 +37490,7 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr"/>
@@ -50345,7 +50345,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>San Joaquin Memorial High School</t>
+          <t>San Joaquin Memorial</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">

--- a/data/customer-import/tier2_invented_parents.xlsx
+++ b/data/customer-import/tier2_invented_parents.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Upload'!$A$1:$Z$545</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$E$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Upload'!$A$1:$Z$541</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z545"/>
+  <dimension ref="A1:Z541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -43723,12 +43723,12 @@
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>St. Francis High School</t>
+          <t>Steele Canyon High School</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
         <is>
-          <t>SFHS</t>
+          <t>SCHS</t>
         </is>
       </c>
       <c r="C489" s="2" t="inlineStr">
@@ -43741,234 +43741,350 @@
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr"/>
       <c r="H489" s="2" t="inlineStr"/>
-      <c r="I489" s="2" t="inlineStr"/>
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
       <c r="J489" s="2" t="inlineStr"/>
-      <c r="K489" s="2" t="inlineStr"/>
-      <c r="L489" s="2" t="inlineStr"/>
-      <c r="M489" s="2" t="inlineStr"/>
-      <c r="N489" s="2" t="inlineStr"/>
+      <c r="K489" s="2" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="L489" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M489" s="2" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="N489" s="2" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
       <c r="O489" s="2" t="inlineStr"/>
-      <c r="P489" s="2" t="inlineStr"/>
-      <c r="Q489" s="2" t="inlineStr"/>
-      <c r="R489" s="2" t="inlineStr"/>
+      <c r="P489" s="2" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="Q489" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R489" s="2" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
       <c r="S489" s="2" t="inlineStr"/>
       <c r="T489" s="2" t="inlineStr"/>
       <c r="U489" s="2" t="inlineStr"/>
       <c r="V489" s="2" t="inlineStr"/>
       <c r="W489" s="2" t="inlineStr">
         <is>
-          <t>Steve Peterson</t>
+          <t>Jered Hunt</t>
         </is>
       </c>
       <c r="X489" s="2" t="inlineStr"/>
       <c r="Y489" s="2" t="inlineStr"/>
       <c r="Z489" s="2" t="inlineStr">
         <is>
-          <t>no customer email; missing structured address</t>
+          <t>no customer email</t>
         </is>
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="inlineStr">
-        <is>
-          <t>St. Francis Flag Football</t>
-        </is>
-      </c>
-      <c r="B490" s="2" t="inlineStr">
-        <is>
-          <t>SFFF</t>
-        </is>
-      </c>
-      <c r="C490" s="2" t="inlineStr">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Steele Canyon HS Baseball</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>SCHB</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D490" s="2" t="inlineStr">
-        <is>
-          <t>St. Francis High School</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr"/>
-      <c r="F490" s="2" t="inlineStr">
-        <is>
-          <t>kketcham@stfrancishs.org</t>
-        </is>
-      </c>
-      <c r="G490" s="2" t="inlineStr"/>
-      <c r="H490" s="2" t="inlineStr"/>
-      <c r="I490" s="2" t="inlineStr"/>
-      <c r="J490" s="2" t="inlineStr"/>
-      <c r="K490" s="2" t="inlineStr"/>
-      <c r="L490" s="2" t="inlineStr"/>
-      <c r="M490" s="2" t="inlineStr"/>
-      <c r="N490" s="2" t="inlineStr"/>
-      <c r="O490" s="2" t="inlineStr"/>
-      <c r="P490" s="2" t="inlineStr"/>
-      <c r="Q490" s="2" t="inlineStr"/>
-      <c r="R490" s="2" t="inlineStr"/>
-      <c r="S490" s="2" t="inlineStr"/>
-      <c r="T490" s="2" t="inlineStr"/>
-      <c r="U490" s="2" t="inlineStr"/>
-      <c r="V490" s="2" t="inlineStr"/>
-      <c r="W490" s="2" t="inlineStr">
-        <is>
-          <t>Steve Peterson</t>
-        </is>
-      </c>
-      <c r="X490" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="Y490" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="Z490" s="2" t="inlineStr">
-        <is>
-          <t>missing structured address</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Steele Canyon High School</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>ddirksen@schscougars.org</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr"/>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr"/>
+      <c r="T490" t="inlineStr"/>
+      <c r="U490" t="inlineStr"/>
+      <c r="V490" t="inlineStr"/>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X490" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="Y490" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="Z490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="inlineStr">
-        <is>
-          <t>St. Francis Store</t>
-        </is>
-      </c>
-      <c r="B491" s="2" t="inlineStr">
-        <is>
-          <t>SFS</t>
-        </is>
-      </c>
-      <c r="C491" s="2" t="inlineStr">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Steele Canyon HS Boy's Soccer</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>SCHBS</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D491" s="2" t="inlineStr">
-        <is>
-          <t>St. Francis High School</t>
-        </is>
-      </c>
-      <c r="E491" s="2" t="inlineStr"/>
-      <c r="F491" s="2" t="inlineStr">
-        <is>
-          <t>kketcham@stfrancishs.org</t>
-        </is>
-      </c>
-      <c r="G491" s="2" t="inlineStr"/>
-      <c r="H491" s="2" t="inlineStr"/>
-      <c r="I491" s="2" t="inlineStr"/>
-      <c r="J491" s="2" t="inlineStr"/>
-      <c r="K491" s="2" t="inlineStr"/>
-      <c r="L491" s="2" t="inlineStr"/>
-      <c r="M491" s="2" t="inlineStr"/>
-      <c r="N491" s="2" t="inlineStr"/>
-      <c r="O491" s="2" t="inlineStr"/>
-      <c r="P491" s="2" t="inlineStr"/>
-      <c r="Q491" s="2" t="inlineStr"/>
-      <c r="R491" s="2" t="inlineStr"/>
-      <c r="S491" s="2" t="inlineStr"/>
-      <c r="T491" s="2" t="inlineStr"/>
-      <c r="U491" s="2" t="inlineStr"/>
-      <c r="V491" s="2" t="inlineStr"/>
-      <c r="W491" s="2" t="inlineStr">
-        <is>
-          <t>Steve Peterson</t>
-        </is>
-      </c>
-      <c r="X491" s="2" t="inlineStr">
-        <is>
-          <t>3336</t>
-        </is>
-      </c>
-      <c r="Y491" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="Z491" s="2" t="inlineStr">
-        <is>
-          <t>missing structured address</t>
-        </is>
-      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Steele Canyon High School</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>jjohnson7119@gmail.com</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr"/>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr"/>
+      <c r="T491" t="inlineStr"/>
+      <c r="U491" t="inlineStr"/>
+      <c r="V491" t="inlineStr"/>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>Mike Mercuriali</t>
+        </is>
+      </c>
+      <c r="X491" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="Y491" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="Z491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="inlineStr">
-        <is>
-          <t>St. Francis Tennis</t>
-        </is>
-      </c>
-      <c r="B492" s="2" t="inlineStr">
-        <is>
-          <t>SFT</t>
-        </is>
-      </c>
-      <c r="C492" s="2" t="inlineStr">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Steele Canyon HS Girl's Volleyball</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>SCHGV</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D492" s="2" t="inlineStr">
-        <is>
-          <t>St. Francis High School</t>
-        </is>
-      </c>
-      <c r="E492" s="2" t="inlineStr"/>
-      <c r="F492" s="2" t="inlineStr">
-        <is>
-          <t>kketcham@stfrancishs.org</t>
-        </is>
-      </c>
-      <c r="G492" s="2" t="inlineStr"/>
-      <c r="H492" s="2" t="inlineStr"/>
-      <c r="I492" s="2" t="inlineStr"/>
-      <c r="J492" s="2" t="inlineStr"/>
-      <c r="K492" s="2" t="inlineStr"/>
-      <c r="L492" s="2" t="inlineStr"/>
-      <c r="M492" s="2" t="inlineStr"/>
-      <c r="N492" s="2" t="inlineStr"/>
-      <c r="O492" s="2" t="inlineStr"/>
-      <c r="P492" s="2" t="inlineStr"/>
-      <c r="Q492" s="2" t="inlineStr"/>
-      <c r="R492" s="2" t="inlineStr"/>
-      <c r="S492" s="2" t="inlineStr"/>
-      <c r="T492" s="2" t="inlineStr"/>
-      <c r="U492" s="2" t="inlineStr"/>
-      <c r="V492" s="2" t="inlineStr"/>
-      <c r="W492" s="2" t="inlineStr">
-        <is>
-          <t>Steve Peterson</t>
-        </is>
-      </c>
-      <c r="X492" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="Y492" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="Z492" s="2" t="inlineStr">
-        <is>
-          <t>missing structured address</t>
-        </is>
-      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Steele Canyon High School</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>wholland@schscougars.org</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>12440 Campo Rd</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr"/>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>91978</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr"/>
+      <c r="T492" t="inlineStr"/>
+      <c r="U492" t="inlineStr"/>
+      <c r="V492" t="inlineStr"/>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X492" t="inlineStr">
+        <is>
+          <t>3642</t>
+        </is>
+      </c>
+      <c r="Y492" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="Z492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>Steele Canyon High School</t>
+          <t>Sweetwater High School</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t>SCHS</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="C493" s="2" t="inlineStr">
@@ -43983,13 +44099,13 @@
       <c r="H493" s="2" t="inlineStr"/>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>12440 Campo Rd</t>
+          <t>2900 Highland Ave</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr"/>
       <c r="K493" s="2" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="L493" s="2" t="inlineStr">
@@ -43999,18 +44115,18 @@
       </c>
       <c r="M493" s="2" t="inlineStr">
         <is>
-          <t>91978</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="N493" s="2" t="inlineStr">
         <is>
-          <t>12440 Campo Rd</t>
+          <t>2900 Highland Ave</t>
         </is>
       </c>
       <c r="O493" s="2" t="inlineStr"/>
       <c r="P493" s="2" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="Q493" s="2" t="inlineStr">
@@ -44020,7 +44136,7 @@
       </c>
       <c r="R493" s="2" t="inlineStr">
         <is>
-          <t>91978</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="S493" s="2" t="inlineStr"/>
@@ -44029,7 +44145,7 @@
       <c r="V493" s="2" t="inlineStr"/>
       <c r="W493" s="2" t="inlineStr">
         <is>
-          <t>Jered Hunt</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
       <c r="X493" s="2" t="inlineStr"/>
@@ -44043,12 +44159,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Steele Canyon HS Baseball</t>
+          <t>Sweetwater High School Boys Soccer</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>SCHB</t>
+          <t>SHSBS</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -44058,26 +44174,26 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Steele Canyon High School</t>
+          <t>Sweetwater High School</t>
         </is>
       </c>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>ddirksen@schscougars.org</t>
+          <t>dvillalvajr@gmail.com</t>
         </is>
       </c>
       <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
       <c r="I494" t="inlineStr">
         <is>
-          <t>12440 Campo Rd</t>
+          <t>2900 Highland Ave</t>
         </is>
       </c>
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -44087,18 +44203,18 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>91978</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t>12440 Campo Rd</t>
+          <t>2900 Highland Ave</t>
         </is>
       </c>
       <c r="O494" t="inlineStr"/>
       <c r="P494" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="Q494" t="inlineStr">
@@ -44108,7 +44224,7 @@
       </c>
       <c r="R494" t="inlineStr">
         <is>
-          <t>91978</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="S494" t="inlineStr"/>
@@ -44117,17 +44233,17 @@
       <c r="V494" t="inlineStr"/>
       <c r="W494" t="inlineStr">
         <is>
-          <t>Jered Hunt</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
       <c r="X494" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="Y494" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="Z494" t="inlineStr"/>
@@ -44135,12 +44251,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Steele Canyon HS Boy's Soccer</t>
+          <t>Sweetwater High School Football</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>SCHBS</t>
+          <t>SHSF</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -44150,26 +44266,26 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Steele Canyon High School</t>
+          <t>Sweetwater High School</t>
         </is>
       </c>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
-          <t>jjohnson7119@gmail.com</t>
+          <t>thomas.cunningham@sweetwaterschools.org</t>
         </is>
       </c>
       <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="inlineStr">
         <is>
-          <t>12440 Campo Rd</t>
+          <t>2900 Highland Ave</t>
         </is>
       </c>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -44179,18 +44295,18 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>91978</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>12440 Campo Rd</t>
+          <t>2900 Highland Ave</t>
         </is>
       </c>
       <c r="O495" t="inlineStr"/>
       <c r="P495" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="Q495" t="inlineStr">
@@ -44200,7 +44316,7 @@
       </c>
       <c r="R495" t="inlineStr">
         <is>
-          <t>91978</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="S495" t="inlineStr"/>
@@ -44214,117 +44330,117 @@
       </c>
       <c r="X495" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="Y495" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="Z495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>Steele Canyon HS Girl's Volleyball</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>SCHGV</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Sweetwater High School Girls Soccer</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>SHSGS</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>Steele Canyon High School</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>wholland@schscougars.org</t>
-        </is>
-      </c>
-      <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
-      <c r="I496" t="inlineStr">
-        <is>
-          <t>12440 Campo Rd</t>
-        </is>
-      </c>
-      <c r="J496" t="inlineStr"/>
-      <c r="K496" t="inlineStr">
-        <is>
-          <t>Spring Valley</t>
-        </is>
-      </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M496" t="inlineStr">
-        <is>
-          <t>91978</t>
-        </is>
-      </c>
-      <c r="N496" t="inlineStr">
-        <is>
-          <t>12440 Campo Rd</t>
-        </is>
-      </c>
-      <c r="O496" t="inlineStr"/>
-      <c r="P496" t="inlineStr">
-        <is>
-          <t>Spring Valley</t>
-        </is>
-      </c>
-      <c r="Q496" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R496" t="inlineStr">
-        <is>
-          <t>91978</t>
-        </is>
-      </c>
-      <c r="S496" t="inlineStr"/>
-      <c r="T496" t="inlineStr"/>
-      <c r="U496" t="inlineStr"/>
-      <c r="V496" t="inlineStr"/>
-      <c r="W496" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X496" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="Y496" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="Z496" t="inlineStr"/>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Sweetwater High School</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr"/>
+      <c r="F496" s="2" t="inlineStr"/>
+      <c r="G496" s="2" t="inlineStr"/>
+      <c r="H496" s="2" t="inlineStr"/>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>2900 Highland Ave</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="inlineStr"/>
+      <c r="K496" s="2" t="inlineStr">
+        <is>
+          <t>National City</t>
+        </is>
+      </c>
+      <c r="L496" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M496" s="2" t="inlineStr">
+        <is>
+          <t>91950</t>
+        </is>
+      </c>
+      <c r="N496" s="2" t="inlineStr">
+        <is>
+          <t>2900 Highland Ave</t>
+        </is>
+      </c>
+      <c r="O496" s="2" t="inlineStr"/>
+      <c r="P496" s="2" t="inlineStr">
+        <is>
+          <t>National City</t>
+        </is>
+      </c>
+      <c r="Q496" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R496" s="2" t="inlineStr">
+        <is>
+          <t>91950</t>
+        </is>
+      </c>
+      <c r="S496" s="2" t="inlineStr"/>
+      <c r="T496" s="2" t="inlineStr"/>
+      <c r="U496" s="2" t="inlineStr"/>
+      <c r="V496" s="2" t="inlineStr"/>
+      <c r="W496" s="2" t="inlineStr">
+        <is>
+          <t>Mike Mercuriali</t>
+        </is>
+      </c>
+      <c r="X496" s="2" t="inlineStr">
+        <is>
+          <t>4134</t>
+        </is>
+      </c>
+      <c r="Y496" s="2" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="Z496" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>Sweetwater High School</t>
+          <t>Troy High School</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>THS</t>
         </is>
       </c>
       <c r="C497" s="2" t="inlineStr">
@@ -44339,13 +44455,13 @@
       <c r="H497" s="2" t="inlineStr"/>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>2900 Highland Ave</t>
+          <t>2200 E Dorothy Lane</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr"/>
       <c r="K497" s="2" t="inlineStr">
         <is>
-          <t>National City</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="L497" s="2" t="inlineStr">
@@ -44355,18 +44471,18 @@
       </c>
       <c r="M497" s="2" t="inlineStr">
         <is>
-          <t>91950</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="N497" s="2" t="inlineStr">
         <is>
-          <t>2900 Highland Ave</t>
+          <t>2200 E Dorothy Lane</t>
         </is>
       </c>
       <c r="O497" s="2" t="inlineStr"/>
       <c r="P497" s="2" t="inlineStr">
         <is>
-          <t>National City</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="Q497" s="2" t="inlineStr">
@@ -44376,7 +44492,7 @@
       </c>
       <c r="R497" s="2" t="inlineStr">
         <is>
-          <t>91950</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="S497" s="2" t="inlineStr"/>
@@ -44385,7 +44501,7 @@
       <c r="V497" s="2" t="inlineStr"/>
       <c r="W497" s="2" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Aaron Mason</t>
         </is>
       </c>
       <c r="X497" s="2" t="inlineStr"/>
@@ -44399,12 +44515,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Sweetwater High School Boys Soccer</t>
+          <t>Troy - NHS</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>SHSBS</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -44414,26 +44530,30 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Sweetwater High School</t>
+          <t>Troy High School</t>
         </is>
       </c>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
-          <t>dvillalvajr@gmail.com</t>
-        </is>
-      </c>
-      <c r="G498" t="inlineStr"/>
+          <t>kgrant@fjuhsd.org</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>(949) 315-1410</t>
+        </is>
+      </c>
       <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr">
         <is>
-          <t>2900 Highland Ave</t>
+          <t>2200 Dorothy Ln.</t>
         </is>
       </c>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr">
         <is>
-          <t>National City</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -44443,18 +44563,18 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>91950</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>2900 Highland Ave</t>
+          <t>2200 Dorothy Ln.</t>
         </is>
       </c>
       <c r="O498" t="inlineStr"/>
       <c r="P498" t="inlineStr">
         <is>
-          <t>National City</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="Q498" t="inlineStr">
@@ -44464,7 +44584,7 @@
       </c>
       <c r="R498" t="inlineStr">
         <is>
-          <t>91950</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="S498" t="inlineStr"/>
@@ -44473,294 +44593,298 @@
       <c r="V498" t="inlineStr"/>
       <c r="W498" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Aaron Mason</t>
         </is>
       </c>
       <c r="X498" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y498" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="Z498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Sweetwater High School Football</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>SHSF</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>Troy Basketball</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>Sweetwater High School</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>thomas.cunningham@sweetwaterschools.org</t>
-        </is>
-      </c>
-      <c r="G499" t="inlineStr"/>
-      <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr">
-        <is>
-          <t>2900 Highland Ave</t>
-        </is>
-      </c>
-      <c r="J499" t="inlineStr"/>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>National City</t>
-        </is>
-      </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M499" t="inlineStr">
-        <is>
-          <t>91950</t>
-        </is>
-      </c>
-      <c r="N499" t="inlineStr">
-        <is>
-          <t>2900 Highland Ave</t>
-        </is>
-      </c>
-      <c r="O499" t="inlineStr"/>
-      <c r="P499" t="inlineStr">
-        <is>
-          <t>National City</t>
-        </is>
-      </c>
-      <c r="Q499" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R499" t="inlineStr">
-        <is>
-          <t>91950</t>
-        </is>
-      </c>
-      <c r="S499" t="inlineStr"/>
-      <c r="T499" t="inlineStr"/>
-      <c r="U499" t="inlineStr"/>
-      <c r="V499" t="inlineStr"/>
-      <c r="W499" t="inlineStr">
-        <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X499" t="inlineStr">
-        <is>
-          <t>4842</t>
-        </is>
-      </c>
-      <c r="Y499" t="inlineStr">
-        <is>
-          <t>5054</t>
-        </is>
-      </c>
-      <c r="Z499" t="inlineStr"/>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>Troy High School</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr"/>
+      <c r="F499" s="2" t="inlineStr"/>
+      <c r="G499" s="2" t="inlineStr"/>
+      <c r="H499" s="2" t="inlineStr"/>
+      <c r="I499" s="2" t="inlineStr">
+        <is>
+          <t>2200 E Dorothy Lane</t>
+        </is>
+      </c>
+      <c r="J499" s="2" t="inlineStr"/>
+      <c r="K499" s="2" t="inlineStr">
+        <is>
+          <t>Fullerton</t>
+        </is>
+      </c>
+      <c r="L499" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M499" s="2" t="inlineStr">
+        <is>
+          <t>92831</t>
+        </is>
+      </c>
+      <c r="N499" s="2" t="inlineStr">
+        <is>
+          <t>2200 E Dorothy Lane</t>
+        </is>
+      </c>
+      <c r="O499" s="2" t="inlineStr"/>
+      <c r="P499" s="2" t="inlineStr">
+        <is>
+          <t>Fullerton</t>
+        </is>
+      </c>
+      <c r="Q499" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R499" s="2" t="inlineStr">
+        <is>
+          <t>92831</t>
+        </is>
+      </c>
+      <c r="S499" s="2" t="inlineStr"/>
+      <c r="T499" s="2" t="inlineStr"/>
+      <c r="U499" s="2" t="inlineStr"/>
+      <c r="V499" s="2" t="inlineStr"/>
+      <c r="W499" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Mason</t>
+        </is>
+      </c>
+      <c r="X499" s="2" t="inlineStr">
+        <is>
+          <t>3670</t>
+        </is>
+      </c>
+      <c r="Y499" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="Z499" s="2" t="inlineStr">
+        <is>
+          <t>no customer email; had NSA-internal email (aaron@nationalsportsapparel.com)</t>
+        </is>
+      </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="inlineStr">
-        <is>
-          <t>Sweetwater High School Girls Soccer</t>
-        </is>
-      </c>
-      <c r="B500" s="2" t="inlineStr">
-        <is>
-          <t>SHSGS</t>
-        </is>
-      </c>
-      <c r="C500" s="2" t="inlineStr">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Troy Boys Golf</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>TBG</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D500" s="2" t="inlineStr">
-        <is>
-          <t>Sweetwater High School</t>
-        </is>
-      </c>
-      <c r="E500" s="2" t="inlineStr"/>
-      <c r="F500" s="2" t="inlineStr"/>
-      <c r="G500" s="2" t="inlineStr"/>
-      <c r="H500" s="2" t="inlineStr"/>
-      <c r="I500" s="2" t="inlineStr">
-        <is>
-          <t>2900 Highland Ave</t>
-        </is>
-      </c>
-      <c r="J500" s="2" t="inlineStr"/>
-      <c r="K500" s="2" t="inlineStr">
-        <is>
-          <t>National City</t>
-        </is>
-      </c>
-      <c r="L500" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M500" s="2" t="inlineStr">
-        <is>
-          <t>91950</t>
-        </is>
-      </c>
-      <c r="N500" s="2" t="inlineStr">
-        <is>
-          <t>2900 Highland Ave</t>
-        </is>
-      </c>
-      <c r="O500" s="2" t="inlineStr"/>
-      <c r="P500" s="2" t="inlineStr">
-        <is>
-          <t>National City</t>
-        </is>
-      </c>
-      <c r="Q500" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R500" s="2" t="inlineStr">
-        <is>
-          <t>91950</t>
-        </is>
-      </c>
-      <c r="S500" s="2" t="inlineStr"/>
-      <c r="T500" s="2" t="inlineStr"/>
-      <c r="U500" s="2" t="inlineStr"/>
-      <c r="V500" s="2" t="inlineStr"/>
-      <c r="W500" s="2" t="inlineStr">
-        <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X500" s="2" t="inlineStr">
-        <is>
-          <t>4134</t>
-        </is>
-      </c>
-      <c r="Y500" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="Z500" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Troy High School</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>sblake@fjuhsd.org</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>2200 E. Dorothy Ln.</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Fullerton</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>92831</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>2200 E. Dorothy Ln.</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr"/>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Fullerton</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>92831</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr"/>
+      <c r="T500" t="inlineStr"/>
+      <c r="U500" t="inlineStr"/>
+      <c r="V500" t="inlineStr"/>
+      <c r="W500" t="inlineStr">
+        <is>
+          <t>Aaron Mason</t>
+        </is>
+      </c>
+      <c r="X500" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="Y500" t="inlineStr"/>
+      <c r="Z500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="inlineStr">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Troy Girls Golf</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>TGG</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
         <is>
           <t>Troy High School</t>
         </is>
       </c>
-      <c r="B501" s="2" t="inlineStr">
-        <is>
-          <t>THS</t>
-        </is>
-      </c>
-      <c r="C501" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D501" s="2" t="inlineStr"/>
-      <c r="E501" s="2" t="inlineStr"/>
-      <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr"/>
-      <c r="H501" s="2" t="inlineStr"/>
-      <c r="I501" s="2" t="inlineStr">
-        <is>
-          <t>2200 E Dorothy Lane</t>
-        </is>
-      </c>
-      <c r="J501" s="2" t="inlineStr"/>
-      <c r="K501" s="2" t="inlineStr">
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>sblake@fjuhsd.org</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>2200 E. Dorothy Ln.</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
         <is>
           <t>Fullerton</t>
         </is>
       </c>
-      <c r="L501" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M501" s="2" t="inlineStr">
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
         <is>
           <t>92831</t>
         </is>
       </c>
-      <c r="N501" s="2" t="inlineStr">
-        <is>
-          <t>2200 E Dorothy Lane</t>
-        </is>
-      </c>
-      <c r="O501" s="2" t="inlineStr"/>
-      <c r="P501" s="2" t="inlineStr">
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>2200 E. Dorothy Ln.</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr"/>
+      <c r="P501" t="inlineStr">
         <is>
           <t>Fullerton</t>
         </is>
       </c>
-      <c r="Q501" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R501" s="2" t="inlineStr">
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
         <is>
           <t>92831</t>
         </is>
       </c>
-      <c r="S501" s="2" t="inlineStr"/>
-      <c r="T501" s="2" t="inlineStr"/>
-      <c r="U501" s="2" t="inlineStr"/>
-      <c r="V501" s="2" t="inlineStr"/>
-      <c r="W501" s="2" t="inlineStr">
+      <c r="S501" t="inlineStr"/>
+      <c r="T501" t="inlineStr"/>
+      <c r="U501" t="inlineStr"/>
+      <c r="V501" t="inlineStr"/>
+      <c r="W501" t="inlineStr">
         <is>
           <t>Aaron Mason</t>
         </is>
       </c>
-      <c r="X501" s="2" t="inlineStr"/>
-      <c r="Y501" s="2" t="inlineStr"/>
-      <c r="Z501" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>3735</t>
+        </is>
+      </c>
+      <c r="Y501" t="inlineStr"/>
+      <c r="Z501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Troy - NHS</t>
+          <t>Troy HS Boys Soccer</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>THBS</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -44776,18 +44900,14 @@
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr">
         <is>
-          <t>kgrant@fjuhsd.org</t>
-        </is>
-      </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>(949) 315-1410</t>
-        </is>
-      </c>
+          <t>lmaldonado@fjuhsd.org</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="inlineStr">
         <is>
-          <t>2200 Dorothy Ln.</t>
+          <t>2200 Dorothy Lane</t>
         </is>
       </c>
       <c r="J502" t="inlineStr"/>
@@ -44808,7 +44928,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t>2200 Dorothy Ln.</t>
+          <t>2200 Dorothy Lane</t>
         </is>
       </c>
       <c r="O502" t="inlineStr"/>
@@ -44833,210 +44953,214 @@
       <c r="V502" t="inlineStr"/>
       <c r="W502" t="inlineStr">
         <is>
-          <t>Aaron Mason</t>
+          <t>Jered Hunt</t>
         </is>
       </c>
       <c r="X502" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="Y502" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="Z502" t="inlineStr"/>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="inlineStr">
-        <is>
-          <t>Troy Basketball</t>
-        </is>
-      </c>
-      <c r="B503" s="2" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="C503" s="2" t="inlineStr">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Troy HS Flag Football</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>THFF</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D503" s="2" t="inlineStr">
+      <c r="D503" t="inlineStr">
         <is>
           <t>Troy High School</t>
         </is>
       </c>
-      <c r="E503" s="2" t="inlineStr"/>
-      <c r="F503" s="2" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr"/>
-      <c r="H503" s="2" t="inlineStr"/>
-      <c r="I503" s="2" t="inlineStr">
-        <is>
-          <t>2200 E Dorothy Lane</t>
-        </is>
-      </c>
-      <c r="J503" s="2" t="inlineStr"/>
-      <c r="K503" s="2" t="inlineStr">
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>dshirota@fjuhsd.org</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>2200 Dorothy Ave</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
         <is>
           <t>Fullerton</t>
         </is>
       </c>
-      <c r="L503" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M503" s="2" t="inlineStr">
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
         <is>
           <t>92831</t>
         </is>
       </c>
-      <c r="N503" s="2" t="inlineStr">
-        <is>
-          <t>2200 E Dorothy Lane</t>
-        </is>
-      </c>
-      <c r="O503" s="2" t="inlineStr"/>
-      <c r="P503" s="2" t="inlineStr">
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>2200 Dorothy Ave</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr"/>
+      <c r="P503" t="inlineStr">
         <is>
           <t>Fullerton</t>
         </is>
       </c>
-      <c r="Q503" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R503" s="2" t="inlineStr">
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
         <is>
           <t>92831</t>
         </is>
       </c>
-      <c r="S503" s="2" t="inlineStr"/>
-      <c r="T503" s="2" t="inlineStr"/>
-      <c r="U503" s="2" t="inlineStr"/>
-      <c r="V503" s="2" t="inlineStr"/>
-      <c r="W503" s="2" t="inlineStr">
-        <is>
-          <t>Aaron Mason</t>
-        </is>
-      </c>
-      <c r="X503" s="2" t="inlineStr">
-        <is>
-          <t>3670</t>
-        </is>
-      </c>
-      <c r="Y503" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="Z503" s="2" t="inlineStr">
-        <is>
-          <t>no customer email; had NSA-internal email (aaron@nationalsportsapparel.com)</t>
-        </is>
-      </c>
+      <c r="S503" t="inlineStr"/>
+      <c r="T503" t="inlineStr"/>
+      <c r="U503" t="inlineStr"/>
+      <c r="V503" t="inlineStr"/>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="Y503" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="Z503" t="inlineStr"/>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>Troy Boys Golf</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>TBG</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>Troy HS Football</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>THF</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr">
+      <c r="D504" s="2" t="inlineStr">
         <is>
           <t>Troy High School</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>sblake@fjuhsd.org</t>
-        </is>
-      </c>
-      <c r="G504" t="inlineStr"/>
-      <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>2200 E. Dorothy Ln.</t>
-        </is>
-      </c>
-      <c r="J504" t="inlineStr"/>
-      <c r="K504" t="inlineStr">
+      <c r="E504" s="2" t="inlineStr"/>
+      <c r="F504" s="2" t="inlineStr"/>
+      <c r="G504" s="2" t="inlineStr"/>
+      <c r="H504" s="2" t="inlineStr"/>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>2200 Dorothy Lane</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="inlineStr"/>
+      <c r="K504" s="2" t="inlineStr">
         <is>
           <t>Fullerton</t>
         </is>
       </c>
-      <c r="L504" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M504" t="inlineStr">
+      <c r="L504" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M504" s="2" t="inlineStr">
         <is>
           <t>92831</t>
         </is>
       </c>
-      <c r="N504" t="inlineStr">
-        <is>
-          <t>2200 E. Dorothy Ln.</t>
-        </is>
-      </c>
-      <c r="O504" t="inlineStr"/>
-      <c r="P504" t="inlineStr">
+      <c r="N504" s="2" t="inlineStr">
+        <is>
+          <t>2200 Dorothy Lane</t>
+        </is>
+      </c>
+      <c r="O504" s="2" t="inlineStr"/>
+      <c r="P504" s="2" t="inlineStr">
         <is>
           <t>Fullerton</t>
         </is>
       </c>
-      <c r="Q504" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R504" t="inlineStr">
+      <c r="Q504" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R504" s="2" t="inlineStr">
         <is>
           <t>92831</t>
         </is>
       </c>
-      <c r="S504" t="inlineStr"/>
-      <c r="T504" t="inlineStr"/>
-      <c r="U504" t="inlineStr"/>
-      <c r="V504" t="inlineStr"/>
-      <c r="W504" t="inlineStr">
-        <is>
-          <t>Aaron Mason</t>
-        </is>
-      </c>
-      <c r="X504" t="inlineStr">
-        <is>
-          <t>3682</t>
-        </is>
-      </c>
-      <c r="Y504" t="inlineStr"/>
-      <c r="Z504" t="inlineStr"/>
+      <c r="S504" s="2" t="inlineStr"/>
+      <c r="T504" s="2" t="inlineStr"/>
+      <c r="U504" s="2" t="inlineStr"/>
+      <c r="V504" s="2" t="inlineStr"/>
+      <c r="W504" s="2" t="inlineStr">
+        <is>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X504" s="2" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="Y504" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="Z504" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Troy Girls Golf</t>
+          <t>Troy HS Girl's Volleyball</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>TGG</t>
+          <t>THGV</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -45052,14 +45176,14 @@
       <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr">
         <is>
-          <t>sblake@fjuhsd.org</t>
+          <t>megan.tomicic@gmail.com</t>
         </is>
       </c>
       <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="inlineStr">
         <is>
-          <t>2200 E. Dorothy Ln.</t>
+          <t>2200 E Dorothy Lane</t>
         </is>
       </c>
       <c r="J505" t="inlineStr"/>
@@ -45080,7 +45204,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t>2200 E. Dorothy Ln.</t>
+          <t>2200 E Dorothy Lane</t>
         </is>
       </c>
       <c r="O505" t="inlineStr"/>
@@ -45105,12 +45229,12 @@
       <c r="V505" t="inlineStr"/>
       <c r="W505" t="inlineStr">
         <is>
-          <t>Aaron Mason</t>
+          <t>Steve Peterson</t>
         </is>
       </c>
       <c r="X505" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="Y505" t="inlineStr"/>
@@ -45119,12 +45243,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Troy HS Boys Soccer</t>
+          <t>Troy HS Wrestling</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>THBS</t>
+          <t>THW</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -45140,14 +45264,14 @@
       <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr">
         <is>
-          <t>lmaldonado@fjuhsd.org</t>
+          <t>AllysOCBoutique@yahoo.com</t>
         </is>
       </c>
       <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr"/>
       <c r="I506" t="inlineStr">
         <is>
-          <t>2200 Dorothy Lane</t>
+          <t>2200 Dorothy Ln</t>
         </is>
       </c>
       <c r="J506" t="inlineStr"/>
@@ -45168,7 +45292,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t>2200 Dorothy Lane</t>
+          <t>2200 Dorothy Ln</t>
         </is>
       </c>
       <c r="O506" t="inlineStr"/>
@@ -45198,25 +45322,21 @@
       </c>
       <c r="X506" t="inlineStr">
         <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="Y506" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
-      </c>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="Y506" t="inlineStr"/>
       <c r="Z506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Troy HS Flag Football</t>
+          <t>Troy Volleyball</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -45232,14 +45352,14 @@
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr">
         <is>
-          <t>dshirota@fjuhsd.org</t>
+          <t>tlendeen@fjuhsd.org</t>
         </is>
       </c>
       <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr"/>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2200 Dorothy Ave</t>
+          <t>2200 E Dorothy Lane</t>
         </is>
       </c>
       <c r="J507" t="inlineStr"/>
@@ -45260,7 +45380,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>2200 Dorothy Ave</t>
+          <t>2200 E Dorothy Lane</t>
         </is>
       </c>
       <c r="O507" t="inlineStr"/>
@@ -45290,50 +45410,42 @@
       </c>
       <c r="X507" t="inlineStr">
         <is>
-          <t>3695</t>
-        </is>
-      </c>
-      <c r="Y507" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>Troy HS Football</t>
+          <t>Tustin High School</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
         <is>
-          <t>THF</t>
+          <t>THS</t>
         </is>
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D508" s="2" t="inlineStr">
-        <is>
-          <t>Troy High School</t>
-        </is>
-      </c>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr"/>
       <c r="E508" s="2" t="inlineStr"/>
       <c r="F508" s="2" t="inlineStr"/>
       <c r="G508" s="2" t="inlineStr"/>
       <c r="H508" s="2" t="inlineStr"/>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>2200 Dorothy Lane</t>
+          <t>1171 El Camino Real</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr"/>
       <c r="K508" s="2" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="L508" s="2" t="inlineStr">
@@ -45343,18 +45455,18 @@
       </c>
       <c r="M508" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="N508" s="2" t="inlineStr">
         <is>
-          <t>2200 Dorothy Lane</t>
+          <t>1171 El Camino Real</t>
         </is>
       </c>
       <c r="O508" s="2" t="inlineStr"/>
       <c r="P508" s="2" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="Q508" s="2" t="inlineStr">
@@ -45364,7 +45476,7 @@
       </c>
       <c r="R508" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="S508" s="2" t="inlineStr"/>
@@ -45376,16 +45488,8 @@
           <t>Jered Hunt</t>
         </is>
       </c>
-      <c r="X508" s="2" t="inlineStr">
-        <is>
-          <t>4172</t>
-        </is>
-      </c>
-      <c r="Y508" s="2" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
-      </c>
+      <c r="X508" s="2" t="inlineStr"/>
+      <c r="Y508" s="2" t="inlineStr"/>
       <c r="Z508" s="2" t="inlineStr">
         <is>
           <t>no customer email</t>
@@ -45395,12 +45499,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Troy HS Girl's Volleyball</t>
+          <t>Tustin HS Girl's Soccer</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>THGV</t>
+          <t>THGS</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -45410,26 +45514,30 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Troy High School</t>
+          <t>Tustin High School</t>
         </is>
       </c>
       <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
         <is>
-          <t>megan.tomicic@gmail.com</t>
-        </is>
-      </c>
-      <c r="G509" t="inlineStr"/>
+          <t>mtrout@tustin.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>(714) 552-6102</t>
+        </is>
+      </c>
       <c r="H509" t="inlineStr"/>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2200 E Dorothy Lane</t>
+          <t>1171 El Camino Real</t>
         </is>
       </c>
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -45439,18 +45547,18 @@
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>2200 E Dorothy Lane</t>
+          <t>1171 El Camino Real</t>
         </is>
       </c>
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="Q509" t="inlineStr">
@@ -45460,7 +45568,7 @@
       </c>
       <c r="R509" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="S509" t="inlineStr"/>
@@ -45469,12 +45577,12 @@
       <c r="V509" t="inlineStr"/>
       <c r="W509" t="inlineStr">
         <is>
-          <t>Steve Peterson</t>
+          <t>Jered Hunt</t>
         </is>
       </c>
       <c r="X509" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="Y509" t="inlineStr"/>
@@ -45483,12 +45591,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Troy HS Wrestling</t>
+          <t>Tustin HS Mens Soccer</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>THW</t>
+          <t>THMS</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -45498,26 +45606,26 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Troy High School</t>
+          <t>Tustin High School</t>
         </is>
       </c>
       <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
-          <t>AllysOCBoutique@yahoo.com</t>
+          <t>najerahec8@gmail.com</t>
         </is>
       </c>
       <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
       <c r="I510" t="inlineStr">
         <is>
-          <t>2200 Dorothy Ln</t>
+          <t>1171 El Camino Real</t>
         </is>
       </c>
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -45527,18 +45635,18 @@
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t>2200 Dorothy Ln</t>
+          <t>1171 El Camino Real</t>
         </is>
       </c>
       <c r="O510" t="inlineStr"/>
       <c r="P510" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="Q510" t="inlineStr">
@@ -45548,7 +45656,7 @@
       </c>
       <c r="R510" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>92780</t>
         </is>
       </c>
       <c r="S510" t="inlineStr"/>
@@ -45562,394 +45670,394 @@
       </c>
       <c r="X510" t="inlineStr">
         <is>
-          <t>2711</t>
-        </is>
-      </c>
-      <c r="Y510" t="inlineStr"/>
+          <t>3725</t>
+        </is>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
       <c r="Z510" t="inlineStr"/>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Troy Volleyball</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>University City College</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>UCC</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D511" s="2" t="inlineStr"/>
+      <c r="E511" s="2" t="inlineStr"/>
+      <c r="F511" s="2" t="inlineStr"/>
+      <c r="G511" s="2" t="inlineStr"/>
+      <c r="H511" s="2" t="inlineStr"/>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>6949 Genesee Ave</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="inlineStr"/>
+      <c r="K511" s="2" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="L511" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M511" s="2" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="N511" s="2" t="inlineStr">
+        <is>
+          <t>6949 Genesee Ave</t>
+        </is>
+      </c>
+      <c r="O511" s="2" t="inlineStr"/>
+      <c r="P511" s="2" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="Q511" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R511" s="2" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="S511" s="2" t="inlineStr"/>
+      <c r="T511" s="2" t="inlineStr"/>
+      <c r="U511" s="2" t="inlineStr"/>
+      <c r="V511" s="2" t="inlineStr"/>
+      <c r="W511" s="2" t="inlineStr">
+        <is>
+          <t>Mike Mercuriali</t>
+        </is>
+      </c>
+      <c r="X511" s="2" t="inlineStr"/>
+      <c r="Y511" s="2" t="inlineStr"/>
+      <c r="Z511" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>University City High School Girls Soccer</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>UCHSGS</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>Troy High School</t>
-        </is>
-      </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>tlendeen@fjuhsd.org</t>
-        </is>
-      </c>
-      <c r="G511" t="inlineStr"/>
-      <c r="H511" t="inlineStr"/>
-      <c r="I511" t="inlineStr">
-        <is>
-          <t>2200 E Dorothy Lane</t>
-        </is>
-      </c>
-      <c r="J511" t="inlineStr"/>
-      <c r="K511" t="inlineStr">
-        <is>
-          <t>Fullerton</t>
-        </is>
-      </c>
-      <c r="L511" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M511" t="inlineStr">
-        <is>
-          <t>92831</t>
-        </is>
-      </c>
-      <c r="N511" t="inlineStr">
-        <is>
-          <t>2200 E Dorothy Lane</t>
-        </is>
-      </c>
-      <c r="O511" t="inlineStr"/>
-      <c r="P511" t="inlineStr">
-        <is>
-          <t>Fullerton</t>
-        </is>
-      </c>
-      <c r="Q511" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R511" t="inlineStr">
-        <is>
-          <t>92831</t>
-        </is>
-      </c>
-      <c r="S511" t="inlineStr"/>
-      <c r="T511" t="inlineStr"/>
-      <c r="U511" t="inlineStr"/>
-      <c r="V511" t="inlineStr"/>
-      <c r="W511" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X511" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
-      </c>
-      <c r="Y511" t="inlineStr"/>
-      <c r="Z511" t="inlineStr"/>
-    </row>
-    <row r="512">
-      <c r="A512" s="2" t="inlineStr">
-        <is>
-          <t>Tustin High School</t>
-        </is>
-      </c>
-      <c r="B512" s="2" t="inlineStr">
-        <is>
-          <t>THS</t>
-        </is>
-      </c>
-      <c r="C512" s="2" t="inlineStr">
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>University City College</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>sd.seiders@yahoo.com</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>6949 Genesee Ave</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>6949 Genesee Ave</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr"/>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr"/>
+      <c r="T512" t="inlineStr"/>
+      <c r="U512" t="inlineStr"/>
+      <c r="V512" t="inlineStr"/>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>Mike Mercuriali</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="Z512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>University City High School Soccer</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>UCHSS</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>University City College</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr"/>
+      <c r="F513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr"/>
+      <c r="H513" s="2" t="inlineStr"/>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>6949 Genesee Ave</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr"/>
+      <c r="K513" s="2" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="L513" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M513" s="2" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="N513" s="2" t="inlineStr">
+        <is>
+          <t>6949 Genesee Ave</t>
+        </is>
+      </c>
+      <c r="O513" s="2" t="inlineStr"/>
+      <c r="P513" s="2" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="Q513" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R513" s="2" t="inlineStr">
+        <is>
+          <t>92122</t>
+        </is>
+      </c>
+      <c r="S513" s="2" t="inlineStr"/>
+      <c r="T513" s="2" t="inlineStr"/>
+      <c r="U513" s="2" t="inlineStr"/>
+      <c r="V513" s="2" t="inlineStr"/>
+      <c r="W513" s="2" t="inlineStr">
+        <is>
+          <t>Mike Mercuriali</t>
+        </is>
+      </c>
+      <c r="X513" s="2" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="Y513" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="Z513" s="2" t="inlineStr">
+        <is>
+          <t>no customer email; had NSA-internal email (merc@nationalsportsapparel.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>Valhalla High School</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>VHS</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
         <is>
           <t>parent</t>
         </is>
       </c>
-      <c r="D512" s="2" t="inlineStr"/>
-      <c r="E512" s="2" t="inlineStr"/>
-      <c r="F512" s="2" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr"/>
-      <c r="H512" s="2" t="inlineStr"/>
-      <c r="I512" s="2" t="inlineStr">
-        <is>
-          <t>1171 El Camino Real</t>
-        </is>
-      </c>
-      <c r="J512" s="2" t="inlineStr"/>
-      <c r="K512" s="2" t="inlineStr">
-        <is>
-          <t>Tustin</t>
-        </is>
-      </c>
-      <c r="L512" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M512" s="2" t="inlineStr">
-        <is>
-          <t>92780</t>
-        </is>
-      </c>
-      <c r="N512" s="2" t="inlineStr">
-        <is>
-          <t>1171 El Camino Real</t>
-        </is>
-      </c>
-      <c r="O512" s="2" t="inlineStr"/>
-      <c r="P512" s="2" t="inlineStr">
-        <is>
-          <t>Tustin</t>
-        </is>
-      </c>
-      <c r="Q512" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R512" s="2" t="inlineStr">
-        <is>
-          <t>92780</t>
-        </is>
-      </c>
-      <c r="S512" s="2" t="inlineStr"/>
-      <c r="T512" s="2" t="inlineStr"/>
-      <c r="U512" s="2" t="inlineStr"/>
-      <c r="V512" s="2" t="inlineStr"/>
-      <c r="W512" s="2" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X512" s="2" t="inlineStr"/>
-      <c r="Y512" s="2" t="inlineStr"/>
-      <c r="Z512" s="2" t="inlineStr">
+      <c r="D514" s="2" t="inlineStr"/>
+      <c r="E514" s="2" t="inlineStr"/>
+      <c r="F514" s="2" t="inlineStr"/>
+      <c r="G514" s="2" t="inlineStr"/>
+      <c r="H514" s="2" t="inlineStr"/>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>1725 Hillsdale Rd</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr"/>
+      <c r="K514" s="2" t="inlineStr">
+        <is>
+          <t>El Cajon</t>
+        </is>
+      </c>
+      <c r="L514" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M514" s="2" t="inlineStr">
+        <is>
+          <t>92019</t>
+        </is>
+      </c>
+      <c r="N514" s="2" t="inlineStr">
+        <is>
+          <t>1725 Hillsdale Rd</t>
+        </is>
+      </c>
+      <c r="O514" s="2" t="inlineStr"/>
+      <c r="P514" s="2" t="inlineStr">
+        <is>
+          <t>El Cajon</t>
+        </is>
+      </c>
+      <c r="Q514" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R514" s="2" t="inlineStr">
+        <is>
+          <t>92019</t>
+        </is>
+      </c>
+      <c r="S514" s="2" t="inlineStr"/>
+      <c r="T514" s="2" t="inlineStr"/>
+      <c r="U514" s="2" t="inlineStr"/>
+      <c r="V514" s="2" t="inlineStr"/>
+      <c r="W514" s="2" t="inlineStr">
+        <is>
+          <t>Mike Mercuriali</t>
+        </is>
+      </c>
+      <c r="X514" s="2" t="inlineStr"/>
+      <c r="Y514" s="2" t="inlineStr"/>
+      <c r="Z514" s="2" t="inlineStr">
         <is>
           <t>no customer email</t>
         </is>
       </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>Tustin HS Girl's Soccer</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>THGS</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>Tustin High School</t>
-        </is>
-      </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr">
-        <is>
-          <t>mtrout@tustin.k12.ca.us</t>
-        </is>
-      </c>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>(714) 552-6102</t>
-        </is>
-      </c>
-      <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr">
-        <is>
-          <t>1171 El Camino Real</t>
-        </is>
-      </c>
-      <c r="J513" t="inlineStr"/>
-      <c r="K513" t="inlineStr">
-        <is>
-          <t>Tustin</t>
-        </is>
-      </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M513" t="inlineStr">
-        <is>
-          <t>92780</t>
-        </is>
-      </c>
-      <c r="N513" t="inlineStr">
-        <is>
-          <t>1171 El Camino Real</t>
-        </is>
-      </c>
-      <c r="O513" t="inlineStr"/>
-      <c r="P513" t="inlineStr">
-        <is>
-          <t>Tustin</t>
-        </is>
-      </c>
-      <c r="Q513" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R513" t="inlineStr">
-        <is>
-          <t>92780</t>
-        </is>
-      </c>
-      <c r="S513" t="inlineStr"/>
-      <c r="T513" t="inlineStr"/>
-      <c r="U513" t="inlineStr"/>
-      <c r="V513" t="inlineStr"/>
-      <c r="W513" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X513" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="Y513" t="inlineStr"/>
-      <c r="Z513" t="inlineStr"/>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>Tustin HS Mens Soccer</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>THMS</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>Tustin High School</t>
-        </is>
-      </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr">
-        <is>
-          <t>najerahec8@gmail.com</t>
-        </is>
-      </c>
-      <c r="G514" t="inlineStr"/>
-      <c r="H514" t="inlineStr"/>
-      <c r="I514" t="inlineStr">
-        <is>
-          <t>1171 El Camino Real</t>
-        </is>
-      </c>
-      <c r="J514" t="inlineStr"/>
-      <c r="K514" t="inlineStr">
-        <is>
-          <t>Tustin</t>
-        </is>
-      </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M514" t="inlineStr">
-        <is>
-          <t>92780</t>
-        </is>
-      </c>
-      <c r="N514" t="inlineStr">
-        <is>
-          <t>1171 El Camino Real</t>
-        </is>
-      </c>
-      <c r="O514" t="inlineStr"/>
-      <c r="P514" t="inlineStr">
-        <is>
-          <t>Tustin</t>
-        </is>
-      </c>
-      <c r="Q514" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R514" t="inlineStr">
-        <is>
-          <t>92780</t>
-        </is>
-      </c>
-      <c r="S514" t="inlineStr"/>
-      <c r="T514" t="inlineStr"/>
-      <c r="U514" t="inlineStr"/>
-      <c r="V514" t="inlineStr"/>
-      <c r="W514" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X514" t="inlineStr">
-        <is>
-          <t>3725</t>
-        </is>
-      </c>
-      <c r="Y514" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="Z514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>University City College</t>
+          <t>Valhalla Athletics</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>UCC</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D515" s="2" t="inlineStr"/>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>Valhalla High School</t>
+        </is>
+      </c>
       <c r="E515" s="2" t="inlineStr"/>
       <c r="F515" s="2" t="inlineStr"/>
       <c r="G515" s="2" t="inlineStr"/>
       <c r="H515" s="2" t="inlineStr"/>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>6949 Genesee Ave</t>
+          <t>1725 Hillsdale Rd</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr"/>
       <c r="K515" s="2" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Cajon</t>
         </is>
       </c>
       <c r="L515" s="2" t="inlineStr">
@@ -45959,18 +46067,18 @@
       </c>
       <c r="M515" s="2" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>92019</t>
         </is>
       </c>
       <c r="N515" s="2" t="inlineStr">
         <is>
-          <t>6949 Genesee Ave</t>
+          <t>1725 Hillsdale Rd</t>
         </is>
       </c>
       <c r="O515" s="2" t="inlineStr"/>
       <c r="P515" s="2" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Cajon</t>
         </is>
       </c>
       <c r="Q515" s="2" t="inlineStr">
@@ -45980,7 +46088,7 @@
       </c>
       <c r="R515" s="2" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>92019</t>
         </is>
       </c>
       <c r="S515" s="2" t="inlineStr"/>
@@ -45992,23 +46100,31 @@
           <t>Mike Mercuriali</t>
         </is>
       </c>
-      <c r="X515" s="2" t="inlineStr"/>
-      <c r="Y515" s="2" t="inlineStr"/>
+      <c r="X515" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="Y515" s="2" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
       <c r="Z515" s="2" t="inlineStr">
         <is>
-          <t>no customer email</t>
+          <t>no customer email; had NSA-internal email (merc@nationalsportsapparel.com)</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>University City High School Girls Soccer</t>
+          <t>Valhalla Boys Soccer</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>UCHSGS</t>
+          <t>VBS</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -46018,26 +46134,26 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>University City College</t>
+          <t>Valhalla High School</t>
         </is>
       </c>
       <c r="E516" t="inlineStr"/>
       <c r="F516" t="inlineStr">
         <is>
-          <t>sd.seiders@yahoo.com</t>
+          <t>setapart4jc@me.com</t>
         </is>
       </c>
       <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr"/>
       <c r="I516" t="inlineStr">
         <is>
-          <t>6949 Genesee Ave</t>
+          <t>1725 Hillsdale Rd</t>
         </is>
       </c>
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Cajon</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -46047,18 +46163,18 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>92019</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>6949 Genesee Ave</t>
+          <t>1725 Hillsdale Rd</t>
         </is>
       </c>
       <c r="O516" t="inlineStr"/>
       <c r="P516" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Cajon</t>
         </is>
       </c>
       <c r="Q516" t="inlineStr">
@@ -46068,7 +46184,7 @@
       </c>
       <c r="R516" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>92019</t>
         </is>
       </c>
       <c r="S516" t="inlineStr"/>
@@ -46082,222 +46198,230 @@
       </c>
       <c r="X516" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="Y516" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="Z516" t="inlineStr"/>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="inlineStr">
-        <is>
-          <t>University City High School Soccer</t>
-        </is>
-      </c>
-      <c r="B517" s="2" t="inlineStr">
-        <is>
-          <t>UCHSS</t>
-        </is>
-      </c>
-      <c r="C517" s="2" t="inlineStr">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Valhalla Girl's Soccer</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>VGS</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D517" s="2" t="inlineStr">
-        <is>
-          <t>University City College</t>
-        </is>
-      </c>
-      <c r="E517" s="2" t="inlineStr"/>
-      <c r="F517" s="2" t="inlineStr"/>
-      <c r="G517" s="2" t="inlineStr"/>
-      <c r="H517" s="2" t="inlineStr"/>
-      <c r="I517" s="2" t="inlineStr">
-        <is>
-          <t>6949 Genesee Ave</t>
-        </is>
-      </c>
-      <c r="J517" s="2" t="inlineStr"/>
-      <c r="K517" s="2" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="L517" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M517" s="2" t="inlineStr">
-        <is>
-          <t>92122</t>
-        </is>
-      </c>
-      <c r="N517" s="2" t="inlineStr">
-        <is>
-          <t>6949 Genesee Ave</t>
-        </is>
-      </c>
-      <c r="O517" s="2" t="inlineStr"/>
-      <c r="P517" s="2" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="Q517" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R517" s="2" t="inlineStr">
-        <is>
-          <t>92122</t>
-        </is>
-      </c>
-      <c r="S517" s="2" t="inlineStr"/>
-      <c r="T517" s="2" t="inlineStr"/>
-      <c r="U517" s="2" t="inlineStr"/>
-      <c r="V517" s="2" t="inlineStr"/>
-      <c r="W517" s="2" t="inlineStr">
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Valhalla High School</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>setapart4jc@me.com</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>1725 Hillsdale Rd</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>El Cajon</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>92019</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>1725 Hillsdale Rd</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr"/>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>El Cajon</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>92019</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr"/>
+      <c r="T517" t="inlineStr"/>
+      <c r="U517" t="inlineStr"/>
+      <c r="V517" t="inlineStr"/>
+      <c r="W517" t="inlineStr">
         <is>
           <t>Mike Mercuriali</t>
         </is>
       </c>
-      <c r="X517" s="2" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="Y517" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="Z517" s="2" t="inlineStr">
-        <is>
-          <t>no customer email; had NSA-internal email (merc@nationalsportsapparel.com)</t>
-        </is>
-      </c>
+      <c r="X517" t="inlineStr">
+        <is>
+          <t>3923</t>
+        </is>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="Z517" t="inlineStr"/>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="inlineStr">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Valhalla HS Girls Lacrosse</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>VHGL</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
         <is>
           <t>Valhalla High School</t>
         </is>
       </c>
-      <c r="B518" s="2" t="inlineStr">
-        <is>
-          <t>VHS</t>
-        </is>
-      </c>
-      <c r="C518" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D518" s="2" t="inlineStr"/>
-      <c r="E518" s="2" t="inlineStr"/>
-      <c r="F518" s="2" t="inlineStr"/>
-      <c r="G518" s="2" t="inlineStr"/>
-      <c r="H518" s="2" t="inlineStr"/>
-      <c r="I518" s="2" t="inlineStr">
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>bupham@guhsd.net</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr">
         <is>
           <t>1725 Hillsdale Rd</t>
         </is>
       </c>
-      <c r="J518" s="2" t="inlineStr"/>
-      <c r="K518" s="2" t="inlineStr">
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
         <is>
           <t>El Cajon</t>
         </is>
       </c>
-      <c r="L518" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M518" s="2" t="inlineStr">
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
         <is>
           <t>92019</t>
         </is>
       </c>
-      <c r="N518" s="2" t="inlineStr">
+      <c r="N518" t="inlineStr">
         <is>
           <t>1725 Hillsdale Rd</t>
         </is>
       </c>
-      <c r="O518" s="2" t="inlineStr"/>
-      <c r="P518" s="2" t="inlineStr">
+      <c r="O518" t="inlineStr"/>
+      <c r="P518" t="inlineStr">
         <is>
           <t>El Cajon</t>
         </is>
       </c>
-      <c r="Q518" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R518" s="2" t="inlineStr">
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
         <is>
           <t>92019</t>
         </is>
       </c>
-      <c r="S518" s="2" t="inlineStr"/>
-      <c r="T518" s="2" t="inlineStr"/>
-      <c r="U518" s="2" t="inlineStr"/>
-      <c r="V518" s="2" t="inlineStr"/>
-      <c r="W518" s="2" t="inlineStr">
+      <c r="S518" t="inlineStr"/>
+      <c r="T518" t="inlineStr"/>
+      <c r="U518" t="inlineStr"/>
+      <c r="V518" t="inlineStr"/>
+      <c r="W518" t="inlineStr">
         <is>
           <t>Mike Mercuriali</t>
         </is>
       </c>
-      <c r="X518" s="2" t="inlineStr"/>
-      <c r="Y518" s="2" t="inlineStr"/>
-      <c r="Z518" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
+      <c r="X518" t="inlineStr">
+        <is>
+          <t>4294</t>
+        </is>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+      <c r="Z518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>Valhalla Athletics</t>
+          <t>Vanguard University</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D519" s="2" t="inlineStr">
-        <is>
-          <t>Valhalla High School</t>
-        </is>
-      </c>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr"/>
       <c r="E519" s="2" t="inlineStr"/>
       <c r="F519" s="2" t="inlineStr"/>
       <c r="G519" s="2" t="inlineStr"/>
       <c r="H519" s="2" t="inlineStr"/>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Dr,</t>
         </is>
       </c>
       <c r="J519" s="2" t="inlineStr"/>
       <c r="K519" s="2" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="L519" s="2" t="inlineStr">
@@ -46307,18 +46431,18 @@
       </c>
       <c r="M519" s="2" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="N519" s="2" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Dr,</t>
         </is>
       </c>
       <c r="O519" s="2" t="inlineStr"/>
       <c r="P519" s="2" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="Q519" s="2" t="inlineStr">
@@ -46328,7 +46452,7 @@
       </c>
       <c r="R519" s="2" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="S519" s="2" t="inlineStr"/>
@@ -46337,34 +46461,26 @@
       <c r="V519" s="2" t="inlineStr"/>
       <c r="W519" s="2" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X519" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="Y519" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
+          <t>Gayle Peterson</t>
+        </is>
+      </c>
+      <c r="X519" s="2" t="inlineStr"/>
+      <c r="Y519" s="2" t="inlineStr"/>
       <c r="Z519" s="2" t="inlineStr">
         <is>
-          <t>no customer email; had NSA-internal email (merc@nationalsportsapparel.com)</t>
+          <t>no customer email</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Valhalla Boys Soccer</t>
+          <t>Vanguard Athletics</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>VBS</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -46374,26 +46490,30 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Valhalla High School</t>
+          <t>Vanguard University</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr">
         <is>
-          <t>setapart4jc@me.com</t>
-        </is>
-      </c>
-      <c r="G520" t="inlineStr"/>
+          <t>ally.garrett@vanguard.edu</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>(714) 619-6620</t>
+        </is>
+      </c>
       <c r="H520" t="inlineStr"/>
       <c r="I520" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Dr,</t>
         </is>
       </c>
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -46403,18 +46523,18 @@
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Dr,</t>
         </is>
       </c>
       <c r="O520" t="inlineStr"/>
       <c r="P520" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="Q520" t="inlineStr">
@@ -46424,7 +46544,7 @@
       </c>
       <c r="R520" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="S520" t="inlineStr"/>
@@ -46433,17 +46553,17 @@
       <c r="V520" t="inlineStr"/>
       <c r="W520" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Gayle Peterson</t>
         </is>
       </c>
       <c r="X520" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="Y520" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="Z520" t="inlineStr"/>
@@ -46451,12 +46571,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Valhalla Girl's Soccer</t>
+          <t>Vanguard Baseball</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>VGS</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -46466,26 +46586,26 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Valhalla High School</t>
+          <t>Vanguard University</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr">
         <is>
-          <t>setapart4jc@me.com</t>
+          <t>robert.pegg@vanguard.edu</t>
         </is>
       </c>
       <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Drive</t>
         </is>
       </c>
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -46495,18 +46615,18 @@
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Drive</t>
         </is>
       </c>
       <c r="O521" t="inlineStr"/>
       <c r="P521" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="Q521" t="inlineStr">
@@ -46516,7 +46636,7 @@
       </c>
       <c r="R521" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="S521" t="inlineStr"/>
@@ -46525,30 +46645,26 @@
       <c r="V521" t="inlineStr"/>
       <c r="W521" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Gayle Peterson</t>
         </is>
       </c>
       <c r="X521" t="inlineStr">
         <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="Y521" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="Y521" t="inlineStr"/>
       <c r="Z521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Valhalla HS Girls Lacrosse</t>
+          <t>Vanguard Beach Volleyball</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>VHGL</t>
+          <t>VBV</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -46558,26 +46674,26 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Valhalla High School</t>
+          <t>Vanguard University</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr">
         <is>
-          <t>bupham@guhsd.net</t>
+          <t>Kris.Dorn@vanguard.edu</t>
         </is>
       </c>
       <c r="G522" t="inlineStr"/>
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Drive</t>
         </is>
       </c>
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -46587,18 +46703,18 @@
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t>1725 Hillsdale Rd</t>
+          <t>55 Fair Drive</t>
         </is>
       </c>
       <c r="O522" t="inlineStr"/>
       <c r="P522" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="Q522" t="inlineStr">
@@ -46608,7 +46724,7 @@
       </c>
       <c r="R522" t="inlineStr">
         <is>
-          <t>92019</t>
+          <t>92626</t>
         </is>
       </c>
       <c r="S522" t="inlineStr"/>
@@ -46617,206 +46733,194 @@
       <c r="V522" t="inlineStr"/>
       <c r="W522" t="inlineStr">
         <is>
+          <t>Gayle Peterson</t>
+        </is>
+      </c>
+      <c r="X522" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="Y522" t="inlineStr"/>
+      <c r="Z522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Vanguard Softball</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Vanguard University</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>nicole.thomas@vanguard.edu</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>55 Fair Drive</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Costa Mesa</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>92626</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>55 Fair Drive</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr"/>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>Costa Mesa</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>92626</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr"/>
+      <c r="T523" t="inlineStr"/>
+      <c r="U523" t="inlineStr"/>
+      <c r="V523" t="inlineStr"/>
+      <c r="W523" t="inlineStr">
+        <is>
+          <t>Gayle Peterson</t>
+        </is>
+      </c>
+      <c r="X523" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="Y523" t="inlineStr"/>
+      <c r="Z523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Walnut High School</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr"/>
+      <c r="E524" s="2" t="inlineStr"/>
+      <c r="F524" s="2" t="inlineStr"/>
+      <c r="G524" s="2" t="inlineStr"/>
+      <c r="H524" s="2" t="inlineStr"/>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>Address: 400 Pierre Rd</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="inlineStr"/>
+      <c r="K524" s="2" t="inlineStr">
+        <is>
+          <t>Walnut</t>
+        </is>
+      </c>
+      <c r="L524" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M524" s="2" t="inlineStr">
+        <is>
+          <t>91789</t>
+        </is>
+      </c>
+      <c r="N524" s="2" t="inlineStr">
+        <is>
+          <t>Address: 400 Pierre Rd</t>
+        </is>
+      </c>
+      <c r="O524" s="2" t="inlineStr"/>
+      <c r="P524" s="2" t="inlineStr">
+        <is>
+          <t>Walnut</t>
+        </is>
+      </c>
+      <c r="Q524" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R524" s="2" t="inlineStr">
+        <is>
+          <t>91789</t>
+        </is>
+      </c>
+      <c r="S524" s="2" t="inlineStr"/>
+      <c r="T524" s="2" t="inlineStr"/>
+      <c r="U524" s="2" t="inlineStr"/>
+      <c r="V524" s="2" t="inlineStr"/>
+      <c r="W524" s="2" t="inlineStr">
+        <is>
           <t>Mike Mercuriali</t>
         </is>
       </c>
-      <c r="X522" t="inlineStr">
-        <is>
-          <t>4294</t>
-        </is>
-      </c>
-      <c r="Y522" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="Z522" t="inlineStr"/>
-    </row>
-    <row r="523">
-      <c r="A523" s="2" t="inlineStr">
-        <is>
-          <t>Vanguard High School</t>
-        </is>
-      </c>
-      <c r="B523" s="2" t="inlineStr">
-        <is>
-          <t>VHS</t>
-        </is>
-      </c>
-      <c r="C523" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D523" s="2" t="inlineStr"/>
-      <c r="E523" s="2" t="inlineStr"/>
-      <c r="F523" s="2" t="inlineStr"/>
-      <c r="G523" s="2" t="inlineStr"/>
-      <c r="H523" s="2" t="inlineStr"/>
-      <c r="I523" s="2" t="inlineStr">
-        <is>
-          <t>55 Fair Dr,</t>
-        </is>
-      </c>
-      <c r="J523" s="2" t="inlineStr"/>
-      <c r="K523" s="2" t="inlineStr">
-        <is>
-          <t>Costa Mesa</t>
-        </is>
-      </c>
-      <c r="L523" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M523" s="2" t="inlineStr">
-        <is>
-          <t>92626</t>
-        </is>
-      </c>
-      <c r="N523" s="2" t="inlineStr">
-        <is>
-          <t>55 Fair Dr,</t>
-        </is>
-      </c>
-      <c r="O523" s="2" t="inlineStr"/>
-      <c r="P523" s="2" t="inlineStr">
-        <is>
-          <t>Costa Mesa</t>
-        </is>
-      </c>
-      <c r="Q523" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R523" s="2" t="inlineStr">
-        <is>
-          <t>92626</t>
-        </is>
-      </c>
-      <c r="S523" s="2" t="inlineStr"/>
-      <c r="T523" s="2" t="inlineStr"/>
-      <c r="U523" s="2" t="inlineStr"/>
-      <c r="V523" s="2" t="inlineStr"/>
-      <c r="W523" s="2" t="inlineStr">
-        <is>
-          <t>Gayle Peterson</t>
-        </is>
-      </c>
-      <c r="X523" s="2" t="inlineStr"/>
-      <c r="Y523" s="2" t="inlineStr"/>
-      <c r="Z523" s="2" t="inlineStr">
+      <c r="X524" s="2" t="inlineStr"/>
+      <c r="Y524" s="2" t="inlineStr"/>
+      <c r="Z524" s="2" t="inlineStr">
         <is>
           <t>no customer email</t>
         </is>
       </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Vanguard Athletics</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>Vanguard High School</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>ally.garrett@vanguard.edu</t>
-        </is>
-      </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>(714) 619-6620</t>
-        </is>
-      </c>
-      <c r="H524" t="inlineStr"/>
-      <c r="I524" t="inlineStr">
-        <is>
-          <t>55 Fair Dr,</t>
-        </is>
-      </c>
-      <c r="J524" t="inlineStr"/>
-      <c r="K524" t="inlineStr">
-        <is>
-          <t>Costa Mesa</t>
-        </is>
-      </c>
-      <c r="L524" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M524" t="inlineStr">
-        <is>
-          <t>92626</t>
-        </is>
-      </c>
-      <c r="N524" t="inlineStr">
-        <is>
-          <t>55 Fair Dr,</t>
-        </is>
-      </c>
-      <c r="O524" t="inlineStr"/>
-      <c r="P524" t="inlineStr">
-        <is>
-          <t>Costa Mesa</t>
-        </is>
-      </c>
-      <c r="Q524" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R524" t="inlineStr">
-        <is>
-          <t>92626</t>
-        </is>
-      </c>
-      <c r="S524" t="inlineStr"/>
-      <c r="T524" t="inlineStr"/>
-      <c r="U524" t="inlineStr"/>
-      <c r="V524" t="inlineStr"/>
-      <c r="W524" t="inlineStr">
-        <is>
-          <t>Gayle Peterson</t>
-        </is>
-      </c>
-      <c r="X524" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="Y524" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="Z524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Vanguard Baseball</t>
+          <t>Walnut HS Boys Soccer</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>VB</t>
+          <t>WHBS</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -46826,26 +46930,26 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Vanguard High School</t>
+          <t>Walnut High School</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr">
         <is>
-          <t>robert.pegg@vanguard.edu</t>
+          <t>drampen0791@gmail.com</t>
         </is>
       </c>
       <c r="G525" t="inlineStr"/>
       <c r="H525" t="inlineStr"/>
       <c r="I525" t="inlineStr">
         <is>
-          <t>55 Fair Drive</t>
+          <t>Address: 400 Pierre Rd</t>
         </is>
       </c>
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr">
         <is>
-          <t>Costa Mesa</t>
+          <t>Walnut</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -46855,18 +46959,18 @@
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>91789</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>55 Fair Drive</t>
+          <t>Address: 400 Pierre Rd</t>
         </is>
       </c>
       <c r="O525" t="inlineStr"/>
       <c r="P525" t="inlineStr">
         <is>
-          <t>Costa Mesa</t>
+          <t>Walnut</t>
         </is>
       </c>
       <c r="Q525" t="inlineStr">
@@ -46876,7 +46980,7 @@
       </c>
       <c r="R525" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>91789</t>
         </is>
       </c>
       <c r="S525" t="inlineStr"/>
@@ -46885,26 +46989,30 @@
       <c r="V525" t="inlineStr"/>
       <c r="W525" t="inlineStr">
         <is>
-          <t>Gayle Peterson</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
       <c r="X525" t="inlineStr">
         <is>
-          <t>2722</t>
-        </is>
-      </c>
-      <c r="Y525" t="inlineStr"/>
+          <t>3965</t>
+        </is>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
       <c r="Z525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Vanguard Beach Volleyball</t>
+          <t>Walnut HS Girls Soccer</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>VBV</t>
+          <t>WHGS</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -46914,26 +47022,26 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Vanguard High School</t>
+          <t>Walnut High School</t>
         </is>
       </c>
       <c r="E526" t="inlineStr"/>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Kris.Dorn@vanguard.edu</t>
+          <t>coachmannyb@outlook.com</t>
         </is>
       </c>
       <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr"/>
       <c r="I526" t="inlineStr">
         <is>
-          <t>55 Fair Drive</t>
+          <t>400 Pierre Rd</t>
         </is>
       </c>
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr">
         <is>
-          <t>Costa Mesa</t>
+          <t>Walnut</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -46943,18 +47051,18 @@
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>91789</t>
         </is>
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t>55 Fair Drive</t>
+          <t>400 Pierre Rd</t>
         </is>
       </c>
       <c r="O526" t="inlineStr"/>
       <c r="P526" t="inlineStr">
         <is>
-          <t>Costa Mesa</t>
+          <t>Walnut</t>
         </is>
       </c>
       <c r="Q526" t="inlineStr">
@@ -46964,7 +47072,7 @@
       </c>
       <c r="R526" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>91789</t>
         </is>
       </c>
       <c r="S526" t="inlineStr"/>
@@ -46973,194 +47081,202 @@
       <c r="V526" t="inlineStr"/>
       <c r="W526" t="inlineStr">
         <is>
-          <t>Gayle Peterson</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
       <c r="X526" t="inlineStr">
         <is>
-          <t>2723</t>
-        </is>
-      </c>
-      <c r="Y526" t="inlineStr"/>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
       <c r="Z526" t="inlineStr"/>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Vanguard Softball</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>Warren High School</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D527" s="2" t="inlineStr"/>
+      <c r="E527" s="2" t="inlineStr"/>
+      <c r="F527" s="2" t="inlineStr"/>
+      <c r="G527" s="2" t="inlineStr"/>
+      <c r="H527" s="2" t="inlineStr"/>
+      <c r="I527" s="2" t="inlineStr">
+        <is>
+          <t>11627 Brookshire Ave</t>
+        </is>
+      </c>
+      <c r="J527" s="2" t="inlineStr"/>
+      <c r="K527" s="2" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="L527" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M527" s="2" t="inlineStr">
+        <is>
+          <t>90241</t>
+        </is>
+      </c>
+      <c r="N527" s="2" t="inlineStr">
+        <is>
+          <t>11627 Brookshire Ave</t>
+        </is>
+      </c>
+      <c r="O527" s="2" t="inlineStr"/>
+      <c r="P527" s="2" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="Q527" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R527" s="2" t="inlineStr">
+        <is>
+          <t>90241</t>
+        </is>
+      </c>
+      <c r="S527" s="2" t="inlineStr"/>
+      <c r="T527" s="2" t="inlineStr"/>
+      <c r="U527" s="2" t="inlineStr"/>
+      <c r="V527" s="2" t="inlineStr"/>
+      <c r="W527" s="2" t="inlineStr">
+        <is>
+          <t>Aaron Mason</t>
+        </is>
+      </c>
+      <c r="X527" s="2" t="inlineStr"/>
+      <c r="Y527" s="2" t="inlineStr"/>
+      <c r="Z527" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Warren HS Girls Basketball</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>WHGB</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>Vanguard High School</t>
-        </is>
-      </c>
-      <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>nicole.thomas@vanguard.edu</t>
-        </is>
-      </c>
-      <c r="G527" t="inlineStr"/>
-      <c r="H527" t="inlineStr"/>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>55 Fair Drive</t>
-        </is>
-      </c>
-      <c r="J527" t="inlineStr"/>
-      <c r="K527" t="inlineStr">
-        <is>
-          <t>Costa Mesa</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M527" t="inlineStr">
-        <is>
-          <t>92626</t>
-        </is>
-      </c>
-      <c r="N527" t="inlineStr">
-        <is>
-          <t>55 Fair Drive</t>
-        </is>
-      </c>
-      <c r="O527" t="inlineStr"/>
-      <c r="P527" t="inlineStr">
-        <is>
-          <t>Costa Mesa</t>
-        </is>
-      </c>
-      <c r="Q527" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R527" t="inlineStr">
-        <is>
-          <t>92626</t>
-        </is>
-      </c>
-      <c r="S527" t="inlineStr"/>
-      <c r="T527" t="inlineStr"/>
-      <c r="U527" t="inlineStr"/>
-      <c r="V527" t="inlineStr"/>
-      <c r="W527" t="inlineStr">
-        <is>
-          <t>Gayle Peterson</t>
-        </is>
-      </c>
-      <c r="X527" t="inlineStr">
-        <is>
-          <t>2724</t>
-        </is>
-      </c>
-      <c r="Y527" t="inlineStr"/>
-      <c r="Z527" t="inlineStr"/>
-    </row>
-    <row r="528">
-      <c r="A528" s="2" t="inlineStr">
-        <is>
-          <t>Walnut High School</t>
-        </is>
-      </c>
-      <c r="B528" s="2" t="inlineStr">
-        <is>
-          <t>WHS</t>
-        </is>
-      </c>
-      <c r="C528" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D528" s="2" t="inlineStr"/>
-      <c r="E528" s="2" t="inlineStr"/>
-      <c r="F528" s="2" t="inlineStr"/>
-      <c r="G528" s="2" t="inlineStr"/>
-      <c r="H528" s="2" t="inlineStr"/>
-      <c r="I528" s="2" t="inlineStr">
-        <is>
-          <t>Address: 400 Pierre Rd</t>
-        </is>
-      </c>
-      <c r="J528" s="2" t="inlineStr"/>
-      <c r="K528" s="2" t="inlineStr">
-        <is>
-          <t>Walnut</t>
-        </is>
-      </c>
-      <c r="L528" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M528" s="2" t="inlineStr">
-        <is>
-          <t>91789</t>
-        </is>
-      </c>
-      <c r="N528" s="2" t="inlineStr">
-        <is>
-          <t>Address: 400 Pierre Rd</t>
-        </is>
-      </c>
-      <c r="O528" s="2" t="inlineStr"/>
-      <c r="P528" s="2" t="inlineStr">
-        <is>
-          <t>Walnut</t>
-        </is>
-      </c>
-      <c r="Q528" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R528" s="2" t="inlineStr">
-        <is>
-          <t>91789</t>
-        </is>
-      </c>
-      <c r="S528" s="2" t="inlineStr"/>
-      <c r="T528" s="2" t="inlineStr"/>
-      <c r="U528" s="2" t="inlineStr"/>
-      <c r="V528" s="2" t="inlineStr"/>
-      <c r="W528" s="2" t="inlineStr">
-        <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X528" s="2" t="inlineStr"/>
-      <c r="Y528" s="2" t="inlineStr"/>
-      <c r="Z528" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Warren High School</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>dangomez@dusd.net</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>(562) 922-4685</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>11627 Brookshire Ave</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>90241</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>11627 Brookshire Ave</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr"/>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>90241</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr"/>
+      <c r="T528" t="inlineStr"/>
+      <c r="U528" t="inlineStr"/>
+      <c r="V528" t="inlineStr"/>
+      <c r="W528" t="inlineStr">
+        <is>
+          <t>Aaron Mason</t>
+        </is>
+      </c>
+      <c r="X528" t="inlineStr">
+        <is>
+          <t>3792</t>
+        </is>
+      </c>
+      <c r="Y528" t="inlineStr"/>
+      <c r="Z528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Walnut HS Boys Soccer</t>
+          <t>Warren HS Track</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>WHBS</t>
+          <t>WHT</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -47170,26 +47286,26 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Walnut High School</t>
+          <t>Warren High School</t>
         </is>
       </c>
       <c r="E529" t="inlineStr"/>
       <c r="F529" t="inlineStr">
         <is>
-          <t>drampen0791@gmail.com</t>
+          <t>danielsingh77@gmail.com</t>
         </is>
       </c>
       <c r="G529" t="inlineStr"/>
       <c r="H529" t="inlineStr"/>
       <c r="I529" t="inlineStr">
         <is>
-          <t>Address: 400 Pierre Rd</t>
+          <t>8141 DePalma St.</t>
         </is>
       </c>
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Walnut</t>
+          <t>Downey</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -47199,18 +47315,18 @@
       </c>
       <c r="M529" t="inlineStr">
         <is>
-          <t>91789</t>
+          <t>90241</t>
         </is>
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t>Address: 400 Pierre Rd</t>
+          <t>8141 DePalma St.</t>
         </is>
       </c>
       <c r="O529" t="inlineStr"/>
       <c r="P529" t="inlineStr">
         <is>
-          <t>Walnut</t>
+          <t>Downey</t>
         </is>
       </c>
       <c r="Q529" t="inlineStr">
@@ -47220,7 +47336,7 @@
       </c>
       <c r="R529" t="inlineStr">
         <is>
-          <t>91789</t>
+          <t>90241</t>
         </is>
       </c>
       <c r="S529" t="inlineStr"/>
@@ -47229,202 +47345,162 @@
       <c r="V529" t="inlineStr"/>
       <c r="W529" t="inlineStr">
         <is>
+          <t>Chase Koissian</t>
+        </is>
+      </c>
+      <c r="X529" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="Y529" t="inlineStr"/>
+      <c r="Z529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>West Hills High School</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>WHHS</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr"/>
+      <c r="E530" s="2" t="inlineStr"/>
+      <c r="F530" s="2" t="inlineStr"/>
+      <c r="G530" s="2" t="inlineStr"/>
+      <c r="H530" s="2" t="inlineStr"/>
+      <c r="I530" s="2" t="inlineStr">
+        <is>
+          <t>8756 Mast Blvd</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="inlineStr"/>
+      <c r="K530" s="2" t="inlineStr">
+        <is>
+          <t>Santee</t>
+        </is>
+      </c>
+      <c r="L530" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="inlineStr">
+        <is>
+          <t>92071</t>
+        </is>
+      </c>
+      <c r="N530" s="2" t="inlineStr">
+        <is>
+          <t>8756 Mast Blvd</t>
+        </is>
+      </c>
+      <c r="O530" s="2" t="inlineStr"/>
+      <c r="P530" s="2" t="inlineStr">
+        <is>
+          <t>Santee</t>
+        </is>
+      </c>
+      <c r="Q530" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R530" s="2" t="inlineStr">
+        <is>
+          <t>92071</t>
+        </is>
+      </c>
+      <c r="S530" s="2" t="inlineStr"/>
+      <c r="T530" s="2" t="inlineStr"/>
+      <c r="U530" s="2" t="inlineStr"/>
+      <c r="V530" s="2" t="inlineStr"/>
+      <c r="W530" s="2" t="inlineStr">
+        <is>
           <t>Mike Mercuriali</t>
         </is>
       </c>
-      <c r="X529" t="inlineStr">
-        <is>
-          <t>3965</t>
-        </is>
-      </c>
-      <c r="Y529" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="Z529" t="inlineStr"/>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>Walnut HS Girls Soccer</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>WHGS</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>Walnut High School</t>
-        </is>
-      </c>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>coachmannyb@outlook.com</t>
-        </is>
-      </c>
-      <c r="G530" t="inlineStr"/>
-      <c r="H530" t="inlineStr"/>
-      <c r="I530" t="inlineStr">
-        <is>
-          <t>400 Pierre Rd</t>
-        </is>
-      </c>
-      <c r="J530" t="inlineStr"/>
-      <c r="K530" t="inlineStr">
-        <is>
-          <t>Walnut</t>
-        </is>
-      </c>
-      <c r="L530" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M530" t="inlineStr">
-        <is>
-          <t>91789</t>
-        </is>
-      </c>
-      <c r="N530" t="inlineStr">
-        <is>
-          <t>400 Pierre Rd</t>
-        </is>
-      </c>
-      <c r="O530" t="inlineStr"/>
-      <c r="P530" t="inlineStr">
-        <is>
-          <t>Walnut</t>
-        </is>
-      </c>
-      <c r="Q530" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R530" t="inlineStr">
-        <is>
-          <t>91789</t>
-        </is>
-      </c>
-      <c r="S530" t="inlineStr"/>
-      <c r="T530" t="inlineStr"/>
-      <c r="U530" t="inlineStr"/>
-      <c r="V530" t="inlineStr"/>
-      <c r="W530" t="inlineStr">
-        <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X530" t="inlineStr">
-        <is>
-          <t>4114</t>
-        </is>
-      </c>
-      <c r="Y530" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="Z530" t="inlineStr"/>
+      <c r="X530" s="2" t="inlineStr"/>
+      <c r="Y530" s="2" t="inlineStr"/>
+      <c r="Z530" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>Warren High School</t>
+          <t>West Hills Cross Country</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>WHS</t>
+          <t>WHCC</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D531" s="2" t="inlineStr"/>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>West Hills High School</t>
+        </is>
+      </c>
       <c r="E531" s="2" t="inlineStr"/>
       <c r="F531" s="2" t="inlineStr"/>
       <c r="G531" s="2" t="inlineStr"/>
       <c r="H531" s="2" t="inlineStr"/>
-      <c r="I531" s="2" t="inlineStr">
-        <is>
-          <t>11627 Brookshire Ave</t>
-        </is>
-      </c>
+      <c r="I531" s="2" t="inlineStr"/>
       <c r="J531" s="2" t="inlineStr"/>
-      <c r="K531" s="2" t="inlineStr">
-        <is>
-          <t>Downey</t>
-        </is>
-      </c>
-      <c r="L531" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M531" s="2" t="inlineStr">
-        <is>
-          <t>90241</t>
-        </is>
-      </c>
-      <c r="N531" s="2" t="inlineStr">
-        <is>
-          <t>11627 Brookshire Ave</t>
-        </is>
-      </c>
+      <c r="K531" s="2" t="inlineStr"/>
+      <c r="L531" s="2" t="inlineStr"/>
+      <c r="M531" s="2" t="inlineStr"/>
+      <c r="N531" s="2" t="inlineStr"/>
       <c r="O531" s="2" t="inlineStr"/>
-      <c r="P531" s="2" t="inlineStr">
-        <is>
-          <t>Downey</t>
-        </is>
-      </c>
-      <c r="Q531" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R531" s="2" t="inlineStr">
-        <is>
-          <t>90241</t>
-        </is>
-      </c>
+      <c r="P531" s="2" t="inlineStr"/>
+      <c r="Q531" s="2" t="inlineStr"/>
+      <c r="R531" s="2" t="inlineStr"/>
       <c r="S531" s="2" t="inlineStr"/>
       <c r="T531" s="2" t="inlineStr"/>
       <c r="U531" s="2" t="inlineStr"/>
       <c r="V531" s="2" t="inlineStr"/>
       <c r="W531" s="2" t="inlineStr">
         <is>
-          <t>Aaron Mason</t>
-        </is>
-      </c>
-      <c r="X531" s="2" t="inlineStr"/>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X531" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
       <c r="Y531" s="2" t="inlineStr"/>
       <c r="Z531" s="2" t="inlineStr">
         <is>
-          <t>no customer email</t>
+          <t>no customer email; missing structured address</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Warren HS Girls Basketball</t>
+          <t>West Hills High School Boys Soccer</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>WHGB</t>
+          <t>WHHSBS</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -47434,30 +47510,26 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Warren High School</t>
+          <t>West Hills High School</t>
         </is>
       </c>
       <c r="E532" t="inlineStr"/>
       <c r="F532" t="inlineStr">
         <is>
-          <t>dangomez@dusd.net</t>
-        </is>
-      </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>(562) 922-4685</t>
-        </is>
-      </c>
+          <t>tvanderhyde@guhsd.net</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr"/>
       <c r="I532" t="inlineStr">
         <is>
-          <t>11627 Brookshire Ave</t>
+          <t>8756 Mast Blvd</t>
         </is>
       </c>
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Downey</t>
+          <t>Santee</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -47467,18 +47539,18 @@
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>90241</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>11627 Brookshire Ave</t>
+          <t>8756 Mast Blvd</t>
         </is>
       </c>
       <c r="O532" t="inlineStr"/>
       <c r="P532" t="inlineStr">
         <is>
-          <t>Downey</t>
+          <t>Santee</t>
         </is>
       </c>
       <c r="Q532" t="inlineStr">
@@ -47488,7 +47560,7 @@
       </c>
       <c r="R532" t="inlineStr">
         <is>
-          <t>90241</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="S532" t="inlineStr"/>
@@ -47497,26 +47569,30 @@
       <c r="V532" t="inlineStr"/>
       <c r="W532" t="inlineStr">
         <is>
-          <t>Aaron Mason</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
       <c r="X532" t="inlineStr">
         <is>
-          <t>3792</t>
-        </is>
-      </c>
-      <c r="Y532" t="inlineStr"/>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
       <c r="Z532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Warren HS Track</t>
+          <t>West Hills High School Girls Soccer</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>WHT</t>
+          <t>WHHSGS</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -47526,26 +47602,26 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Warren High School</t>
+          <t>West Hills High School</t>
         </is>
       </c>
       <c r="E533" t="inlineStr"/>
       <c r="F533" t="inlineStr">
         <is>
-          <t>danielsingh77@gmail.com</t>
+          <t>rpshubert@icloud.com</t>
         </is>
       </c>
       <c r="G533" t="inlineStr"/>
       <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr">
         <is>
-          <t>8141 DePalma St.</t>
+          <t>8756 Mast Blvd</t>
         </is>
       </c>
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Downey</t>
+          <t>Santee</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -47555,18 +47631,18 @@
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>90241</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>8141 DePalma St.</t>
+          <t>8756 Mast Blvd</t>
         </is>
       </c>
       <c r="O533" t="inlineStr"/>
       <c r="P533" t="inlineStr">
         <is>
-          <t>Downey</t>
+          <t>Santee</t>
         </is>
       </c>
       <c r="Q533" t="inlineStr">
@@ -47576,7 +47652,7 @@
       </c>
       <c r="R533" t="inlineStr">
         <is>
-          <t>90241</t>
+          <t>92071</t>
         </is>
       </c>
       <c r="S533" t="inlineStr"/>
@@ -47585,26 +47661,30 @@
       <c r="V533" t="inlineStr"/>
       <c r="W533" t="inlineStr">
         <is>
-          <t>Chase Koissian</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
       <c r="X533" t="inlineStr">
         <is>
-          <t>2727</t>
-        </is>
-      </c>
-      <c r="Y533" t="inlineStr"/>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
       <c r="Z533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>West Hills High School</t>
+          <t>Westcliff College</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>WHHS</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
@@ -47619,13 +47699,13 @@
       <c r="H534" s="2" t="inlineStr"/>
       <c r="I534" s="2" t="inlineStr">
         <is>
-          <t>8756 Mast Blvd</t>
+          <t>16715 Von Karman Ave #100,</t>
         </is>
       </c>
       <c r="J534" s="2" t="inlineStr"/>
       <c r="K534" s="2" t="inlineStr">
         <is>
-          <t>Santee</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="L534" s="2" t="inlineStr">
@@ -47635,18 +47715,18 @@
       </c>
       <c r="M534" s="2" t="inlineStr">
         <is>
-          <t>92071</t>
+          <t>92606</t>
         </is>
       </c>
       <c r="N534" s="2" t="inlineStr">
         <is>
-          <t>8756 Mast Blvd</t>
+          <t>16715 Von Karman Ave #100,</t>
         </is>
       </c>
       <c r="O534" s="2" t="inlineStr"/>
       <c r="P534" s="2" t="inlineStr">
         <is>
-          <t>Santee</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="Q534" s="2" t="inlineStr">
@@ -47656,7 +47736,7 @@
       </c>
       <c r="R534" s="2" t="inlineStr">
         <is>
-          <t>92071</t>
+          <t>92606</t>
         </is>
       </c>
       <c r="S534" s="2" t="inlineStr"/>
@@ -47665,7 +47745,7 @@
       <c r="V534" s="2" t="inlineStr"/>
       <c r="W534" s="2" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Chase Koissian</t>
         </is>
       </c>
       <c r="X534" s="2" t="inlineStr"/>
@@ -47677,334 +47757,362 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="inlineStr">
-        <is>
-          <t>West Hills Cross Country</t>
-        </is>
-      </c>
-      <c r="B535" s="2" t="inlineStr">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Westcliff University Baseball</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>WUB</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Westcliff College</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>davidshermet@westcliff.edu</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>16715 Von Karman Ave #100,</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>92606</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>16715 Von Karman Ave #100,</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr"/>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>92606</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr"/>
+      <c r="T535" t="inlineStr"/>
+      <c r="U535" t="inlineStr"/>
+      <c r="V535" t="inlineStr"/>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>Chase Koissian</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr"/>
+      <c r="Z535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Westcliff University Softball</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>WUS</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Westcliff College</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr"/>
+      <c r="F536" s="2" t="inlineStr"/>
+      <c r="G536" s="2" t="inlineStr"/>
+      <c r="H536" s="2" t="inlineStr"/>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>16715 Von Karman Ave</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr"/>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="L536" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M536" s="2" t="inlineStr">
+        <is>
+          <t>92606</t>
+        </is>
+      </c>
+      <c r="N536" s="2" t="inlineStr">
+        <is>
+          <t>16715 Von Karman Ave</t>
+        </is>
+      </c>
+      <c r="O536" s="2" t="inlineStr"/>
+      <c r="P536" s="2" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="Q536" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R536" s="2" t="inlineStr">
+        <is>
+          <t>92606</t>
+        </is>
+      </c>
+      <c r="S536" s="2" t="inlineStr"/>
+      <c r="T536" s="2" t="inlineStr"/>
+      <c r="U536" s="2" t="inlineStr"/>
+      <c r="V536" s="2" t="inlineStr"/>
+      <c r="W536" s="2" t="inlineStr">
+        <is>
+          <t>Chase Koissian</t>
+        </is>
+      </c>
+      <c r="X536" s="2" t="inlineStr">
+        <is>
+          <t>2733</t>
+        </is>
+      </c>
+      <c r="Y536" s="2" t="inlineStr"/>
+      <c r="Z536" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Westminster High School</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr"/>
+      <c r="E537" s="2" t="inlineStr"/>
+      <c r="F537" s="2" t="inlineStr"/>
+      <c r="G537" s="2" t="inlineStr"/>
+      <c r="H537" s="2" t="inlineStr"/>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest Ave</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr"/>
+      <c r="K537" s="2" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="L537" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M537" s="2" t="inlineStr">
+        <is>
+          <t>92683</t>
+        </is>
+      </c>
+      <c r="N537" s="2" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest Ave</t>
+        </is>
+      </c>
+      <c r="O537" s="2" t="inlineStr"/>
+      <c r="P537" s="2" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="Q537" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R537" s="2" t="inlineStr">
+        <is>
+          <t>92683</t>
+        </is>
+      </c>
+      <c r="S537" s="2" t="inlineStr"/>
+      <c r="T537" s="2" t="inlineStr"/>
+      <c r="U537" s="2" t="inlineStr"/>
+      <c r="V537" s="2" t="inlineStr"/>
+      <c r="W537" s="2" t="inlineStr">
+        <is>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X537" s="2" t="inlineStr"/>
+      <c r="Y537" s="2" t="inlineStr"/>
+      <c r="Z537" s="2" t="inlineStr">
+        <is>
+          <t>no customer email</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Westminster HS Cross Country</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
         <is>
           <t>WHCC</t>
         </is>
       </c>
-      <c r="C535" s="2" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D535" s="2" t="inlineStr">
-        <is>
-          <t>West Hills High School</t>
-        </is>
-      </c>
-      <c r="E535" s="2" t="inlineStr"/>
-      <c r="F535" s="2" t="inlineStr"/>
-      <c r="G535" s="2" t="inlineStr"/>
-      <c r="H535" s="2" t="inlineStr"/>
-      <c r="I535" s="2" t="inlineStr"/>
-      <c r="J535" s="2" t="inlineStr"/>
-      <c r="K535" s="2" t="inlineStr"/>
-      <c r="L535" s="2" t="inlineStr"/>
-      <c r="M535" s="2" t="inlineStr"/>
-      <c r="N535" s="2" t="inlineStr"/>
-      <c r="O535" s="2" t="inlineStr"/>
-      <c r="P535" s="2" t="inlineStr"/>
-      <c r="Q535" s="2" t="inlineStr"/>
-      <c r="R535" s="2" t="inlineStr"/>
-      <c r="S535" s="2" t="inlineStr"/>
-      <c r="T535" s="2" t="inlineStr"/>
-      <c r="U535" s="2" t="inlineStr"/>
-      <c r="V535" s="2" t="inlineStr"/>
-      <c r="W535" s="2" t="inlineStr">
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Westminster High School</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>gmaciel@hbuhsd.edu</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest Ave</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>92683</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest Ave</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr"/>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>92683</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr"/>
+      <c r="T538" t="inlineStr"/>
+      <c r="U538" t="inlineStr"/>
+      <c r="V538" t="inlineStr"/>
+      <c r="W538" t="inlineStr">
         <is>
           <t>Jered Hunt</t>
         </is>
       </c>
-      <c r="X535" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="Y535" s="2" t="inlineStr"/>
-      <c r="Z535" s="2" t="inlineStr">
-        <is>
-          <t>no customer email; missing structured address</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>West Hills High School Boys Soccer</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>WHHSBS</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>West Hills High School</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr">
-        <is>
-          <t>tvanderhyde@guhsd.net</t>
-        </is>
-      </c>
-      <c r="G536" t="inlineStr"/>
-      <c r="H536" t="inlineStr"/>
-      <c r="I536" t="inlineStr">
-        <is>
-          <t>8756 Mast Blvd</t>
-        </is>
-      </c>
-      <c r="J536" t="inlineStr"/>
-      <c r="K536" t="inlineStr">
-        <is>
-          <t>Santee</t>
-        </is>
-      </c>
-      <c r="L536" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M536" t="inlineStr">
-        <is>
-          <t>92071</t>
-        </is>
-      </c>
-      <c r="N536" t="inlineStr">
-        <is>
-          <t>8756 Mast Blvd</t>
-        </is>
-      </c>
-      <c r="O536" t="inlineStr"/>
-      <c r="P536" t="inlineStr">
-        <is>
-          <t>Santee</t>
-        </is>
-      </c>
-      <c r="Q536" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R536" t="inlineStr">
-        <is>
-          <t>92071</t>
-        </is>
-      </c>
-      <c r="S536" t="inlineStr"/>
-      <c r="T536" t="inlineStr"/>
-      <c r="U536" t="inlineStr"/>
-      <c r="V536" t="inlineStr"/>
-      <c r="W536" t="inlineStr">
-        <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X536" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
-      </c>
-      <c r="Y536" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="Z536" t="inlineStr"/>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>West Hills High School Girls Soccer</t>
-        </is>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>WHHSGS</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>West Hills High School</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>rpshubert@icloud.com</t>
-        </is>
-      </c>
-      <c r="G537" t="inlineStr"/>
-      <c r="H537" t="inlineStr"/>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>8756 Mast Blvd</t>
-        </is>
-      </c>
-      <c r="J537" t="inlineStr"/>
-      <c r="K537" t="inlineStr">
-        <is>
-          <t>Santee</t>
-        </is>
-      </c>
-      <c r="L537" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M537" t="inlineStr">
-        <is>
-          <t>92071</t>
-        </is>
-      </c>
-      <c r="N537" t="inlineStr">
-        <is>
-          <t>8756 Mast Blvd</t>
-        </is>
-      </c>
-      <c r="O537" t="inlineStr"/>
-      <c r="P537" t="inlineStr">
-        <is>
-          <t>Santee</t>
-        </is>
-      </c>
-      <c r="Q537" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R537" t="inlineStr">
-        <is>
-          <t>92071</t>
-        </is>
-      </c>
-      <c r="S537" t="inlineStr"/>
-      <c r="T537" t="inlineStr"/>
-      <c r="U537" t="inlineStr"/>
-      <c r="V537" t="inlineStr"/>
-      <c r="W537" t="inlineStr">
-        <is>
-          <t>Mike Mercuriali</t>
-        </is>
-      </c>
-      <c r="X537" t="inlineStr">
-        <is>
-          <t>4132</t>
-        </is>
-      </c>
-      <c r="Y537" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
-      </c>
-      <c r="Z537" t="inlineStr"/>
-    </row>
-    <row r="538">
-      <c r="A538" s="2" t="inlineStr">
-        <is>
-          <t>Westcliff College</t>
-        </is>
-      </c>
-      <c r="B538" s="2" t="inlineStr">
-        <is>
-          <t>WC</t>
-        </is>
-      </c>
-      <c r="C538" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D538" s="2" t="inlineStr"/>
-      <c r="E538" s="2" t="inlineStr"/>
-      <c r="F538" s="2" t="inlineStr"/>
-      <c r="G538" s="2" t="inlineStr"/>
-      <c r="H538" s="2" t="inlineStr"/>
-      <c r="I538" s="2" t="inlineStr">
-        <is>
-          <t>16715 Von Karman Ave #100,</t>
-        </is>
-      </c>
-      <c r="J538" s="2" t="inlineStr"/>
-      <c r="K538" s="2" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="L538" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M538" s="2" t="inlineStr">
-        <is>
-          <t>92606</t>
-        </is>
-      </c>
-      <c r="N538" s="2" t="inlineStr">
-        <is>
-          <t>16715 Von Karman Ave #100,</t>
-        </is>
-      </c>
-      <c r="O538" s="2" t="inlineStr"/>
-      <c r="P538" s="2" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="Q538" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R538" s="2" t="inlineStr">
-        <is>
-          <t>92606</t>
-        </is>
-      </c>
-      <c r="S538" s="2" t="inlineStr"/>
-      <c r="T538" s="2" t="inlineStr"/>
-      <c r="U538" s="2" t="inlineStr"/>
-      <c r="V538" s="2" t="inlineStr"/>
-      <c r="W538" s="2" t="inlineStr">
-        <is>
-          <t>Chase Koissian</t>
-        </is>
-      </c>
-      <c r="X538" s="2" t="inlineStr"/>
-      <c r="Y538" s="2" t="inlineStr"/>
-      <c r="Z538" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
+      <c r="X538" t="inlineStr">
+        <is>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="Z538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Westcliff University Baseball</t>
+          <t>Westminster HS Flag Football</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>WUB</t>
+          <t>WHFF</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -48014,26 +48122,26 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Westcliff College</t>
+          <t>Westminster High School</t>
         </is>
       </c>
       <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr">
         <is>
-          <t>davidshermet@westcliff.edu</t>
+          <t>ealbright@hbuhsd.edu</t>
         </is>
       </c>
       <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr"/>
       <c r="I539" t="inlineStr">
         <is>
-          <t>16715 Von Karman Ave #100,</t>
+          <t>14325 Goldenwest St</t>
         </is>
       </c>
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
@@ -48043,18 +48151,18 @@
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t>92606</t>
+          <t>92683</t>
         </is>
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t>16715 Von Karman Ave #100,</t>
+          <t>14325 Goldenwest St</t>
         </is>
       </c>
       <c r="O539" t="inlineStr"/>
       <c r="P539" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="Q539" t="inlineStr">
@@ -48064,7 +48172,7 @@
       </c>
       <c r="R539" t="inlineStr">
         <is>
-          <t>92606</t>
+          <t>92683</t>
         </is>
       </c>
       <c r="S539" t="inlineStr"/>
@@ -48073,543 +48181,195 @@
       <c r="V539" t="inlineStr"/>
       <c r="W539" t="inlineStr">
         <is>
-          <t>Chase Koissian</t>
+          <t>Jered Hunt</t>
         </is>
       </c>
       <c r="X539" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="Y539" t="inlineStr"/>
       <c r="Z539" t="inlineStr"/>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="inlineStr">
-        <is>
-          <t>Westcliff University Softball</t>
-        </is>
-      </c>
-      <c r="B540" s="2" t="inlineStr">
-        <is>
-          <t>WUS</t>
-        </is>
-      </c>
-      <c r="C540" s="2" t="inlineStr">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Westminster HS Softball</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
         <is>
           <t>sub</t>
         </is>
       </c>
-      <c r="D540" s="2" t="inlineStr">
-        <is>
-          <t>Westcliff College</t>
-        </is>
-      </c>
-      <c r="E540" s="2" t="inlineStr"/>
-      <c r="F540" s="2" t="inlineStr"/>
-      <c r="G540" s="2" t="inlineStr"/>
-      <c r="H540" s="2" t="inlineStr"/>
-      <c r="I540" s="2" t="inlineStr">
-        <is>
-          <t>16715 Von Karman Ave</t>
-        </is>
-      </c>
-      <c r="J540" s="2" t="inlineStr"/>
-      <c r="K540" s="2" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="L540" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M540" s="2" t="inlineStr">
-        <is>
-          <t>92606</t>
-        </is>
-      </c>
-      <c r="N540" s="2" t="inlineStr">
-        <is>
-          <t>16715 Von Karman Ave</t>
-        </is>
-      </c>
-      <c r="O540" s="2" t="inlineStr"/>
-      <c r="P540" s="2" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="Q540" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R540" s="2" t="inlineStr">
-        <is>
-          <t>92606</t>
-        </is>
-      </c>
-      <c r="S540" s="2" t="inlineStr"/>
-      <c r="T540" s="2" t="inlineStr"/>
-      <c r="U540" s="2" t="inlineStr"/>
-      <c r="V540" s="2" t="inlineStr"/>
-      <c r="W540" s="2" t="inlineStr">
-        <is>
-          <t>Chase Koissian</t>
-        </is>
-      </c>
-      <c r="X540" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="Y540" s="2" t="inlineStr"/>
-      <c r="Z540" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Westminster High School</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>ealbright@hbuhsd.edu</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest St</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>92683</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest St</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr"/>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>92683</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr"/>
+      <c r="T540" t="inlineStr"/>
+      <c r="U540" t="inlineStr"/>
+      <c r="V540" t="inlineStr"/>
+      <c r="W540" t="inlineStr">
+        <is>
+          <t>Jered Hunt</t>
+        </is>
+      </c>
+      <c r="X540" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="Y540" t="inlineStr"/>
+      <c r="Z540" t="inlineStr"/>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="inlineStr">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Westminster HS Volleyball</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>WHV</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
         <is>
           <t>Westminster High School</t>
         </is>
       </c>
-      <c r="B541" s="2" t="inlineStr">
-        <is>
-          <t>WHS</t>
-        </is>
-      </c>
-      <c r="C541" s="2" t="inlineStr">
-        <is>
-          <t>parent</t>
-        </is>
-      </c>
-      <c r="D541" s="2" t="inlineStr"/>
-      <c r="E541" s="2" t="inlineStr"/>
-      <c r="F541" s="2" t="inlineStr"/>
-      <c r="G541" s="2" t="inlineStr"/>
-      <c r="H541" s="2" t="inlineStr"/>
-      <c r="I541" s="2" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest Ave</t>
-        </is>
-      </c>
-      <c r="J541" s="2" t="inlineStr"/>
-      <c r="K541" s="2" t="inlineStr">
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>cwebber@hbuhsd.edu</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest St</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
         <is>
           <t>Westminster</t>
         </is>
       </c>
-      <c r="L541" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M541" s="2" t="inlineStr">
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
         <is>
           <t>92683</t>
         </is>
       </c>
-      <c r="N541" s="2" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest Ave</t>
-        </is>
-      </c>
-      <c r="O541" s="2" t="inlineStr"/>
-      <c r="P541" s="2" t="inlineStr">
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>14325 Goldenwest St</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr"/>
+      <c r="P541" t="inlineStr">
         <is>
           <t>Westminster</t>
         </is>
       </c>
-      <c r="Q541" s="2" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R541" s="2" t="inlineStr">
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
         <is>
           <t>92683</t>
         </is>
       </c>
-      <c r="S541" s="2" t="inlineStr"/>
-      <c r="T541" s="2" t="inlineStr"/>
-      <c r="U541" s="2" t="inlineStr"/>
-      <c r="V541" s="2" t="inlineStr"/>
-      <c r="W541" s="2" t="inlineStr">
+      <c r="S541" t="inlineStr"/>
+      <c r="T541" t="inlineStr"/>
+      <c r="U541" t="inlineStr"/>
+      <c r="V541" t="inlineStr"/>
+      <c r="W541" t="inlineStr">
         <is>
           <t>Jered Hunt</t>
         </is>
       </c>
-      <c r="X541" s="2" t="inlineStr"/>
-      <c r="Y541" s="2" t="inlineStr"/>
-      <c r="Z541" s="2" t="inlineStr">
-        <is>
-          <t>no customer email</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>Westminster HS Cross Country</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>WHCC</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>Westminster High School</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>gmaciel@hbuhsd.edu</t>
-        </is>
-      </c>
-      <c r="G542" t="inlineStr"/>
-      <c r="H542" t="inlineStr"/>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest Ave</t>
-        </is>
-      </c>
-      <c r="J542" t="inlineStr"/>
-      <c r="K542" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M542" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="N542" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest Ave</t>
-        </is>
-      </c>
-      <c r="O542" t="inlineStr"/>
-      <c r="P542" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="Q542" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R542" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="S542" t="inlineStr"/>
-      <c r="T542" t="inlineStr"/>
-      <c r="U542" t="inlineStr"/>
-      <c r="V542" t="inlineStr"/>
-      <c r="W542" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X542" t="inlineStr">
-        <is>
-          <t>3836</t>
-        </is>
-      </c>
-      <c r="Y542" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="Z542" t="inlineStr"/>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>Westminster HS Flag Football</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>WHFF</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>Westminster High School</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>ealbright@hbuhsd.edu</t>
-        </is>
-      </c>
-      <c r="G543" t="inlineStr"/>
-      <c r="H543" t="inlineStr"/>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest St</t>
-        </is>
-      </c>
-      <c r="J543" t="inlineStr"/>
-      <c r="K543" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="L543" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M543" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="N543" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest St</t>
-        </is>
-      </c>
-      <c r="O543" t="inlineStr"/>
-      <c r="P543" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="Q543" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R543" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="S543" t="inlineStr"/>
-      <c r="T543" t="inlineStr"/>
-      <c r="U543" t="inlineStr"/>
-      <c r="V543" t="inlineStr"/>
-      <c r="W543" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X543" t="inlineStr">
-        <is>
-          <t>3304</t>
-        </is>
-      </c>
-      <c r="Y543" t="inlineStr"/>
-      <c r="Z543" t="inlineStr"/>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>Westminster HS Softball</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>WHS</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>Westminster High School</t>
-        </is>
-      </c>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>ealbright@hbuhsd.edu</t>
-        </is>
-      </c>
-      <c r="G544" t="inlineStr"/>
-      <c r="H544" t="inlineStr"/>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest St</t>
-        </is>
-      </c>
-      <c r="J544" t="inlineStr"/>
-      <c r="K544" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="L544" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M544" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="N544" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest St</t>
-        </is>
-      </c>
-      <c r="O544" t="inlineStr"/>
-      <c r="P544" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="Q544" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R544" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="S544" t="inlineStr"/>
-      <c r="T544" t="inlineStr"/>
-      <c r="U544" t="inlineStr"/>
-      <c r="V544" t="inlineStr"/>
-      <c r="W544" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X544" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="Y544" t="inlineStr"/>
-      <c r="Z544" t="inlineStr"/>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>Westminster HS Volleyball</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>WHV</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>sub</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Westminster High School</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>cwebber@hbuhsd.edu</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr"/>
-      <c r="I545" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest St</t>
-        </is>
-      </c>
-      <c r="J545" t="inlineStr"/>
-      <c r="K545" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="N545" t="inlineStr">
-        <is>
-          <t>14325 Goldenwest St</t>
-        </is>
-      </c>
-      <c r="O545" t="inlineStr"/>
-      <c r="P545" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="Q545" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="R545" t="inlineStr">
-        <is>
-          <t>92683</t>
-        </is>
-      </c>
-      <c r="S545" t="inlineStr"/>
-      <c r="T545" t="inlineStr"/>
-      <c r="U545" t="inlineStr"/>
-      <c r="V545" t="inlineStr"/>
-      <c r="W545" t="inlineStr">
-        <is>
-          <t>Jered Hunt</t>
-        </is>
-      </c>
-      <c r="X545" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>2736</t>
         </is>
       </c>
-      <c r="Y545" t="inlineStr"/>
-      <c r="Z545" t="inlineStr"/>
+      <c r="Y541" t="inlineStr"/>
+      <c r="Z541" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z545"/>
+  <autoFilter ref="A1:Z541"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48620,7 +48380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50745,29 +50505,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>St. Francis High School</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+          <t>Steele Canyon High School</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Spring Valley</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
       <c r="D86" t="n">
         <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Steve Peterson</t>
+          <t>Jered Hunt, Mike Mercuriali</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Steele Canyon High School</t>
+          <t>Sweetwater High School</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Spring Valley</t>
+          <t>National City</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -50780,19 +50548,19 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jered Hunt, Mike Mercuriali</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sweetwater High School</t>
+          <t>Troy High School</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>National City</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -50801,23 +50569,23 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Aaron Mason, Jered Hunt, Steve Peterson</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Troy High School</t>
+          <t>Tustin High School</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>Tustin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -50826,23 +50594,23 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aaron Mason, Jered Hunt, Steve Peterson</t>
+          <t>Jered Hunt</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tustin High School</t>
+          <t>University City College</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tustin</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -50855,19 +50623,19 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jered Hunt</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>University City College</t>
+          <t>Valhalla High School</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>El Cajon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -50876,7 +50644,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -50887,12 +50655,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Valhalla High School</t>
+          <t>Vanguard University</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>El Cajon</t>
+          <t>Costa Mesa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -50905,19 +50673,19 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Gayle Peterson</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vanguard High School</t>
+          <t>Walnut High School</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Costa Mesa</t>
+          <t>Walnut</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -50926,23 +50694,23 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gayle Peterson</t>
+          <t>Mike Mercuriali</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Walnut High School</t>
+          <t>Warren High School</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Walnut</t>
+          <t>Downey</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -50955,19 +50723,19 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mike Mercuriali</t>
+          <t>Aaron Mason, Chase Koissian</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Warren High School</t>
+          <t>West Hills High School</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Downey</t>
+          <t>Santee</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -50976,23 +50744,23 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aaron Mason, Chase Koissian</t>
+          <t>Jered Hunt, Mike Mercuriali</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>West Hills High School</t>
+          <t>Westcliff College</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Santee</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -51001,23 +50769,23 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jered Hunt, Mike Mercuriali</t>
+          <t>Chase Koissian</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Westcliff College</t>
+          <t>Westminster High School</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Westminster</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -51026,41 +50794,16 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chase Koissian</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Westminster High School</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Westminster</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
           <t>Jered Hunt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E98"/>
+  <autoFilter ref="A1:E97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>